--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.9%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.1%</t>
+          <t>-568.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-259.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-199.7%</t>
+          <t>-179.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.5%</t>
+          <t>-206.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-163.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-103.0%</t>
+          <t>-75.2%</t>
         </is>
       </c>
     </row>
@@ -43868,19 +43868,19 @@
         <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.156088696795822</v>
+        <v>3.330701626026427</v>
       </c>
       <c r="D1840" t="n">
         <v>-0.1508189717609766</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.095404683777685</v>
+        <v>3.270017613008289</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.30545252455241</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.13483507841956</v>
+        <v>3.309448007650164</v>
       </c>
       <c r="D1841" t="n">
         <v>-0.4080130064690334</v>
       </c>
       <c r="E1841" t="n">
-        <v>2.971273451518199</v>
+        <v>3.145886380748803</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>4.129882485351313</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.13585268755003</v>
+        <v>3.310465616780634</v>
       </c>
       <c r="D1842" t="n">
         <v>-0.4737803965184454</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.945984104628904</v>
+        <v>3.120597033859509</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>4.130900094481784</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.126480719537785</v>
+        <v>3.30109364876839</v>
       </c>
       <c r="D1843" t="n">
         <v>-0.67902507357569</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.854514265793762</v>
+        <v>3.029127195024366</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>4.121528126469539</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.116563445493024</v>
+        <v>3.291176374723628</v>
       </c>
       <c r="D1844" t="n">
         <v>-0.7607969740034417</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.8118882315779</v>
+        <v>2.986501160808504</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>4.12783219646846</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.121328762326726</v>
+        <v>3.29594169155733</v>
       </c>
       <c r="D1845" t="n">
         <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.789769905262851</v>
+        <v>2.964382834493455</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>4.132597513302162</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.119153558445966</v>
+        <v>3.29376648767657</v>
       </c>
       <c r="D1846" t="n">
         <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.704568387625446</v>
+        <v>2.879181316856051</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.831269909555831</v>
+        <v>4.005882838786436</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.117080449951029</v>
+        <v>3.291693379181634</v>
       </c>
       <c r="D1847" t="n">
         <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.535393669711775</v>
+        <v>2.710006598942379</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.578544386932792</v>
+        <v>3.753157316163396</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.116946666549951</v>
+        <v>3.291559595780555</v>
       </c>
       <c r="D1848" t="n">
         <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.419207219668524</v>
+        <v>2.593820148899128</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.592859680375822</v>
+        <v>3.767472609606426</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.121838811103876</v>
+        <v>3.296451740334481</v>
       </c>
       <c r="D1849" t="n">
         <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.340897740881218</v>
+        <v>2.515510670111822</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.597751824929747</v>
+        <v>3.772364754160351</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.116920267441865</v>
+        <v>3.291533196672469</v>
       </c>
       <c r="D1850" t="n">
         <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251414228864017</v>
+        <v>2.426027158094621</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.46598582873495</v>
+        <v>3.640598757965554</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.110004566748314</v>
+        <v>3.284617495978918</v>
       </c>
       <c r="D1851" t="n">
         <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098071037312605</v>
+        <v>2.272683966543209</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239428891754608</v>
+        <v>3.414041820985212</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.130342856487082</v>
+        <v>3.304955785717686</v>
       </c>
       <c r="D1852" t="n">
         <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035013014470699</v>
+        <v>2.209625943701303</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.134672712622365</v>
+        <v>3.309285641852969</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.13844160689565</v>
+        <v>3.313054536126255</v>
       </c>
       <c r="D1853" t="n">
         <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944231290973179</v>
+        <v>2.118844220203783</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.154863475130221</v>
+        <v>3.329476404360825</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.139547998939383</v>
+        <v>3.314160928169987</v>
       </c>
       <c r="D1854" t="n">
         <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748383671807272</v>
+        <v>1.922996601037877</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.860538850359495</v>
+        <v>3.0351517795901</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138090537752246</v>
+        <v>3.31270346698285</v>
       </c>
       <c r="D1855" t="n">
         <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592854054248107</v>
+        <v>1.767466983478711</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859081389172359</v>
+        <v>3.033694318402963</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.314472590437466</v>
       </c>
       <c r="D1856" t="n">
         <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49467490569689</v>
+        <v>1.669287834927494</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882608144525252</v>
+        <v>3.057221073755857</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.310578649093724</v>
       </c>
       <c r="D1857" t="n">
         <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.40817625359834</v>
+        <v>1.582789182828944</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.754807137049298</v>
+        <v>2.929420066279902</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.312351575793984</v>
       </c>
       <c r="D1858" t="n">
         <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282211550266398</v>
+        <v>1.456824479497002</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.756580063749557</v>
+        <v>2.931192992980161</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.298684463261388</v>
       </c>
       <c r="D1859" t="n">
         <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.270435049704492</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.835675382582806</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.286969238263479</v>
       </c>
       <c r="D1860" t="n">
         <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>1.164842227053562</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.827761917922449</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.285549829919444</v>
       </c>
       <c r="D1861" t="n">
         <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>1.029157759817346</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.785583918285072</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.292037390153685</v>
       </c>
       <c r="D1862" t="n">
         <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.8901948220914622</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.733138496399038</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.291291905159517</v>
       </c>
       <c r="D1863" t="n">
         <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.7433983840417948</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.554606540825461</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.290053449174276</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.578724417184282</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.308214818531813</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.285238881645737</v>
       </c>
       <c r="D1865" t="n">
         <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.4632794095294099</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.303400251003274</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.283232932254614</v>
       </c>
       <c r="D1866" t="n">
         <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.2947167104234882</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.301394301612151</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.293491622923293</v>
       </c>
       <c r="D1867" t="n">
         <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.2072668408013394</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.31165299228083</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.289591188068988</v>
       </c>
       <c r="D1868" t="n">
         <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>0.1212659982523303</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.307752557426526</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.287996108123989</v>
       </c>
       <c r="D1869" t="n">
         <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>0.05423896703357789</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.306157477481527</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.291775084053197</v>
       </c>
       <c r="D1870" t="n">
         <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.06064659376129322</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.268690571970408</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.287748779518794</v>
       </c>
       <c r="D1871" t="n">
         <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.1393607816194171</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.264664267436005</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.28764667819721</v>
       </c>
       <c r="D1872" t="n">
         <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.292663438438054</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.264562166114421</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.29021819416864</v>
       </c>
       <c r="D1873" t="n">
         <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.3628398388606375</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.15801180749483</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.29556849746669</v>
       </c>
       <c r="D1874" t="n">
         <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.5013016645641879</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.16336211079288</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.303484517423868</v>
       </c>
       <c r="D1875" t="n">
         <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.5135252699886994</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.141068692677524</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.306526268045637</v>
       </c>
       <c r="D1876" t="n">
         <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.5495312303354889</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>2.085538876846455</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.309419824367209</v>
       </c>
       <c r="D1877" t="n">
         <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.6056481092161738</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.999916780364641</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.314933021485851</v>
       </c>
       <c r="D1878" t="n">
         <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.6818381822294768</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.92884661071489</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.319415575970287</v>
       </c>
       <c r="D1879" t="n">
         <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.7070888182491069</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.846509450838522</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.334787277463708</v>
       </c>
       <c r="D1880" t="n">
         <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.6623291840887058</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.905963051332413</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.349342498211225</v>
       </c>
       <c r="D1881" t="n">
         <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.7178237302958062</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.815443621648003</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.342123333309629</v>
       </c>
       <c r="D1882" t="n">
         <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.8188237328031982</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.808224456746407</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.335451142535653</v>
       </c>
       <c r="D1883" t="n">
         <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.867245815987753</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.738927427356564</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.336566932374209</v>
       </c>
       <c r="D1884" t="n">
         <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-0.8872444883893271</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.682637925245682</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.339260661003324</v>
       </c>
       <c r="D1885" t="n">
         <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-0.9349654771075282</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.700482627560642</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.343250996689725</v>
       </c>
       <c r="D1886" t="n">
         <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-0.9101689358336023</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.704472963247043</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.341775769790983</v>
       </c>
       <c r="D1887" t="n">
         <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-0.9683128994219921</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.702997736348301</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.356829179955855</v>
       </c>
       <c r="D1888" t="n">
         <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-0.9334231514871862</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.747805653168073</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.343778046309172</v>
       </c>
       <c r="D1889" t="n">
         <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-0.9413513279319594</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.70544105451605</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.353357119345381</v>
       </c>
       <c r="D1890" t="n">
         <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.8414341938079866</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.740176132904557</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.35449626390144</v>
       </c>
       <c r="D1891" t="n">
         <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.7904635867168914</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.741315277460616</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.357130038063548</v>
       </c>
       <c r="D1892" t="n">
         <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.8089879277724981</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.746922259275791</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.362863742302184</v>
       </c>
       <c r="D1893" t="n">
         <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.7744009534187093</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.752655963514427</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.353126479908319</v>
       </c>
       <c r="D1894" t="n">
         <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.7555916587687159</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.785738536686351</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.343242998595411</v>
       </c>
       <c r="D1895" t="n">
         <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.7280915264875332</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.775855055373444</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.341408438096038</v>
       </c>
       <c r="D1896" t="n">
         <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.6230293666395479</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.77402049487407</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.341108123122577</v>
       </c>
       <c r="D1897" t="n">
         <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.5841668661424126</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.814511629816943</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.34177662926807</v>
       </c>
       <c r="D1898" t="n">
         <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.5739169436065357</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.829552260548011</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.328516313106318</v>
       </c>
       <c r="D1899" t="n">
         <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.481553284439169</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.974727907379936</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839728</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.325729279446017</v>
       </c>
       <c r="D1900" t="n">
         <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.201508468697535</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.971940873719635</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.326072903333859</v>
       </c>
       <c r="D1901" t="n">
         <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.1850911254632175</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.996395076627191</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.325439724554616</v>
       </c>
       <c r="D1902" t="n">
         <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.1203643558667151</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>2.093801820411566</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.333364153392468</v>
       </c>
       <c r="D1903" t="n">
         <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.01904743813702314</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.241814982587178</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.330471943079509</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>0.03792690795302356</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.29466486701974</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.325839429826536</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>0.08620458415240551</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.369397637945299</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.328654490514173</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>0.1513149778639389</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.46565569816878</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.341560831737831</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.2638212385610301</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.478562039392439</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.213584902138613</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>0.09360931305256948</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.287232115929358</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.262129244015699</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>0.1346596940822171</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.332418852010365</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.142250321327531</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>0.07395678795708927</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.224732478867332</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.133536335074053</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>0.0864306106052064</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.247800205966247</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.12657572297896</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>0.09688936121838942</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.240839593871154</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.141038077360103</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.2082110729810758</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.255301948252297</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.135570197819298</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.2460468482892795</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.249834068711492</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.133068291829875</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.2928613962267086</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.321306843612347</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.1407692700672</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.3090220540254114</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.341697341191739</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.136549978414251</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.4023089391658394</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.337478049538789</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.138674292334267</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.4451383811967737</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.347533804494263</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.131416367317969</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.5378206137601054</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.340275879477965</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.135015490838618</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.611776574267727</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.343875002998614</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.78093391139299</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.148342996893172</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.693682665531266</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.460070386866645</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632784</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.147363474509469</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.7224189694428986</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.503664603925946</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.152058275563786</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.75256806739079</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.546540850320624</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.133252534347581</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.7783330299049536</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.52773510910442</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242298</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.134995610972459</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.8762483052517753</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.673736483812213</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.138924924807279</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.9090746463550734</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.677665797647033</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.82232699787997</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.139603508724619</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.9309525591849686</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.711546136965536</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.136601579944613</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.9714725845968526</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.70854420818553</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.138180616955227</v>
       </c>
       <c r="D1929" t="n">
         <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>1.061059940822271</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.794855152236932</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.15407479975705</v>
       </c>
       <c r="D1930" t="n">
         <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>1.130101199249405</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.810749335038755</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.155220644197352</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.179316277035507</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.883999029497757</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.165308746758792</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.247273237636842</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.980890419119039</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.151346238160218</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.209360798095191</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.931003014105849</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.173746731482784</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.26648109052936</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.953403507428416</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.173819132856196</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.26556560931805</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.951994084924744</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.184826055330898</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.249224457263148</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.968566426821175</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.175262763962789</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.946651115301141</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.021632964297981</v>
+        <v>1.196245893528585</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.959003135453067</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.999972329003176</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.977644274629847</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8339452656068858</v>
+        <v>1.00855819483749</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.783712700493453</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>3.004539560994964</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.802170014837378</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9087022015156609</v>
+        <v>1.083315130746265</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.788279932485241</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.980281589756171</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.913106267478627</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8400697292203685</v>
+        <v>1.014682658450973</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.764021961246448</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.983412974976076</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.879442722006345</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8566665326291869</v>
+        <v>1.031279461859791</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.787351473749723</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.993585361408209</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.819590102802621</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8907799667428087</v>
+        <v>1.065392895973413</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.797523860181855</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.988531631982069</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.733346639776244</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.92022362252722</v>
+        <v>1.094836551757824</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.792470130755715</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.980307407426595</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.778653459175223</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8938766702121537</v>
+        <v>1.068489599442758</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.759759808394703</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.980859280459696</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.807686563877525</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8828153013643347</v>
+        <v>1.057428230594939</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.760311681427804</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.910131972351062</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.714876082426665</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8492121858360442</v>
+        <v>1.023825115066648</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.745270662189685</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.912005448275663</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.759265551756092</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8333298740288742</v>
+        <v>1.007942803259478</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.720510456516629</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.907081156787386</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.646594333519842</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8734740698350971</v>
+        <v>1.048086999065701</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.783188895970103</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.912572452618053</v>
       </c>
       <c r="D1949" t="n">
         <v>-4.534217332337169</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9239161661388335</v>
+        <v>1.098529095369438</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.78868019180077</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.924069654386592</v>
       </c>
       <c r="D1950" t="n">
         <v>-4.561997730238522</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9243012087468316</v>
+        <v>1.098914137977436</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.783509154828497</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.762425374387245</v>
       </c>
       <c r="D1951" t="n">
         <v>-4.644999011263801</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7294564163373733</v>
+        <v>0.9040693455679776</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.610722344112846</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.882575035106451</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.753613089707132</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8061604456792464</v>
+        <v>0.9807733749098506</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.730872004832052</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190772</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.897088061208774</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.840211672688235</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7860340385891282</v>
+        <v>0.9606469678197325</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.745385030934375</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.74117406991343</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.894507502551142</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.801828010130084</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7988069449547575</v>
+        <v>0.9734198741853617</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.765834669811634</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.75114719753249</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.891236531396444</v>
       </c>
       <c r="D1955" t="n">
         <v>-4.624711680094918</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8663825058141257</v>
+        <v>1.04099543504473</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.762563698656936</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793908</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.891919923158357</v>
       </c>
       <c r="D1956" t="n">
         <v>-4.669803924928464</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8490289996426206</v>
+        <v>1.023641928873225</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.726109464517215</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011241</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.885706898464772</v>
       </c>
       <c r="D1957" t="n">
         <v>-4.490428503689696</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.914566143444542</v>
+        <v>1.089179072675146</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.813962494726061</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.866514353796362</v>
       </c>
       <c r="D1958" t="n">
         <v>-4.535442717210302</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8773679133678893</v>
+        <v>1.051980842598494</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.776560612868888</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509544</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.872205916135307</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.802447227482737</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7762576715978611</v>
+        <v>0.9508706008284653</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.665634352382064</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.871409838031809</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.903645008919909</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7349824809194936</v>
+        <v>0.9095954101500978</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.623792986151374</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.869009799586125</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.871169422749137</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7455726769421192</v>
+        <v>0.9201856061727234</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.621392947705691</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.86553451879437</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.85213129504184</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7497126472332829</v>
+        <v>0.9243255764638871</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.583007500115219</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>3.043116387733051</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.883257926192458</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9148438637117162</v>
+        <v>1.08945679294232</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.7605893690539</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067871</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>3.043949716719184</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.897124687526376</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9101304881642824</v>
+        <v>1.084743417394887</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.73870794799974</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789128</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>3.04995824711611</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.917381986055334</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9080360991496252</v>
+        <v>1.082649028380229</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.744716478396666</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.129110894908132</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.769639015820331</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.046285935035648</v>
+        <v>1.220898864266252</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.924553540529617</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.131904516439613</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.871653698351553</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.008273683554641</v>
+        <v>1.182886612785245</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.927347162061098</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394738</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.132566864831272</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.865500992298768</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011397114367413</v>
+        <v>1.186010043598017</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.931701134084427</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.131647341571382</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.88231029044927</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.003753871847322</v>
+        <v>1.178366801077926</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.920696031934237</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.197982895368203</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.820012291673148</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.095008625154592</v>
+        <v>1.269621554385196</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.987031585731057</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992198</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.906563767757601</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.61822209400799</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8843055766100534</v>
+        <v>1.058918505840658</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.814423373421948</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.976854000079776</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.558331412365397</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9785520815892659</v>
+        <v>1.15316501081987</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746035085499075</v>
+        <v>2.92064801472968</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.99148173619582</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.656071956990371</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9540835998553197</v>
+        <v>1.128696529085924</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751129254735331</v>
+        <v>2.925742183965935</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489392</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.990017717020491</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.8324097171133</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8820844766308196</v>
+        <v>1.056697405861424</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.643862579486245</v>
+        <v>2.818475508716849</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.98850933506042</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.755987670681374</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.911144913243519</v>
+        <v>1.085757842474123</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642354197526173</v>
+        <v>2.816967126756778</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.83602339102497</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.988372202495856</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.711614539042805</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9287570333343826</v>
+        <v>1.103369962564987</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668840943944751</v>
+        <v>2.843453873175355</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.988372202495856</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.703660568748033</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9319386214522916</v>
+        <v>1.106551550682896</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668840943944751</v>
+        <v>2.843453873175355</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.994753959523661</v>
       </c>
       <c r="D1978" t="n">
         <v>-4.656004838186977</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9573826707045185</v>
+        <v>1.131995599935123</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.703816139309189</v>
+        <v>2.878429068539793</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.82270724432688</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.999646332898386</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.528320528392681</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.013348767996962</v>
+        <v>1.187961697227566</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785319098560491</v>
+        <v>2.959932027791095</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.986401005374258</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.588987118795069</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9758368043118786</v>
+        <v>1.150449733542483</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.723054781005243</v>
+        <v>2.897667710235848</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690032</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.990498707984886</v>
       </c>
       <c r="D1981" t="n">
         <v>-4.544148717186671</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9978698675658666</v>
+        <v>1.172482796796471</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.729878543382794</v>
+        <v>2.904491472613398</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674316</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.994659647615964</v>
       </c>
       <c r="D1982" t="n">
         <v>-4.644907352943669</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9617273528941452</v>
+        <v>1.136340282124749</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.23217096101282</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.680744141777669</v>
+        <v>2.855357071008273</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163225</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>3.000539250143802</v>
       </c>
       <c r="D1983" t="n">
         <v>-4.600704515857768</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9852880902563426</v>
+        <v>1.159901019486947</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1879681239269196</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713145446557046</v>
+        <v>2.88775837578765</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022906</v>
+        <v>3.83822866302291</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.998949250613049</v>
       </c>
       <c r="D1984" t="n">
         <v>-4.637683543521211</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9689064796602131</v>
+        <v>1.143519408890817</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.733739788101092</v>
+        <v>2.908352717331696</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86392411404214</v>
+        <v>3.863924114042145</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>3.050197015796089</v>
       </c>
       <c r="D1985" t="n">
         <v>-4.657741622386052</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.012131013297316</v>
+        <v>1.186743942527921</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.784987553284132</v>
+        <v>2.959600482514736</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078283</v>
+        <v>3.865367715078287</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>3.048637720390342</v>
       </c>
       <c r="D1986" t="n">
         <v>-4.617810949208161</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.026543987162726</v>
+        <v>1.20115691639333</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1110635489576987</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.807386661785118</v>
+        <v>2.981999591015723</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.8645188762324</v>
+        <v>3.864518876232404</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>3.043585948628612</v>
       </c>
       <c r="D1987" t="n">
         <v>-4.566778856485634</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.041905052490007</v>
+        <v>1.216517981720611</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.06003145623517075</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.832954145656906</v>
+        <v>3.00756707488751</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.84257639416212</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>3.060773352721317</v>
       </c>
       <c r="D1988" t="n">
         <v>-4.501554675358428</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.085182129033594</v>
+        <v>1.259795058264198</v>
       </c>
       <c r="F1988" t="n">
         <v>0.005192724892034872</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.889276058425934</v>
+        <v>3.063888987656538</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.840090220639824</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>3.056734325020597</v>
       </c>
       <c r="D1989" t="n">
         <v>-4.464127655287294</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.096113909361328</v>
+        <v>1.270726838591932</v>
       </c>
       <c r="F1989" t="n">
         <v>0.01044426292121653</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.888387953542723</v>
+        <v>3.063000882773327</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749924</v>
+        <v>3.845198842749928</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>3.057991117351837</v>
       </c>
       <c r="D1990" t="n">
         <v>-4.484239311322002</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.089326039278685</v>
+        <v>1.263938968509289</v>
       </c>
       <c r="F1990" t="n">
         <v>0.02147160791863573</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.896261152872415</v>
+        <v>3.070874082103019</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.828690479393555</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.218548888373048</v>
       </c>
       <c r="D1991" t="n">
         <v>-4.430494496894798</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.271381736070778</v>
+        <v>1.445994665301382</v>
       </c>
       <c r="F1991" t="n">
         <v>0.03153491735909769</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.062856909557903</v>
+        <v>3.237469838788507</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714888</v>
+        <v>3.813251854714893</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.338661797590865</v>
       </c>
       <c r="D1992" t="n">
         <v>-4.406702928288656</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.401011272731052</v>
+        <v>1.575624201961656</v>
       </c>
       <c r="F1992" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197244759939406</v>
+        <v>3.37185768917001</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.814259761756018</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.330369773604724</v>
       </c>
       <c r="D1993" t="n">
         <v>-4.380618844024847</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.403152882450434</v>
+        <v>1.577765811681038</v>
       </c>
       <c r="F1993" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.188952735953265</v>
+        <v>3.363565665183869</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654193</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.328562969188504</v>
       </c>
       <c r="D1994" t="n">
         <v>-4.3762845409678</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.403079799257033</v>
+        <v>1.577692728487637</v>
       </c>
       <c r="F1994" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278135993528566</v>
+        <v>3.452748922759171</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717123</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.346117374915295</v>
       </c>
       <c r="D1995" t="n">
         <v>-4.367392079574516</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.424191189541137</v>
+        <v>1.598804118771741</v>
       </c>
       <c r="F1995" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.295690399255358</v>
+        <v>3.470303328485962</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702631</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.337972422319879</v>
       </c>
       <c r="D1996" t="n">
         <v>-4.535868196544394</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.34865579015777</v>
+        <v>1.523268719388374</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1790287535678631</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.270776745229993</v>
+        <v>3.445389674460597</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539974</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.408385083776723</v>
       </c>
       <c r="D1997" t="n">
         <v>-3.838068667682811</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.698188263159247</v>
+        <v>1.872801192389851</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.298980571064591</v>
+        <v>3.473593500295195</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389904</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.399049106273627</v>
       </c>
       <c r="D1998" t="n">
         <v>-3.815347563999658</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.697940727129413</v>
+        <v>1.872553656360017</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.289644593561495</v>
+        <v>3.464257522792099</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534942</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.383342302894192</v>
+        <v>3.557955232124796</v>
       </c>
       <c r="D1999" t="n">
         <v>-3.955640163536851</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.800729813165705</v>
+        <v>1.975342742396309</v>
       </c>
       <c r="F1999" t="n">
         <v>-0.03161190533974023</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.364375159690348</v>
+        <v>3.538988088920953</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.77996275940168</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.420420125387839</v>
+        <v>3.595033054618443</v>
       </c>
       <c r="D2000" t="n">
         <v>-4.110421170315106</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.775895232948049</v>
+        <v>1.950508162178654</v>
       </c>
       <c r="F2000" t="n">
         <v>-0.06497957939421634</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.381432377751309</v>
+        <v>3.556045306981913</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557228</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.417095481377384</v>
+        <v>3.591708410607988</v>
       </c>
       <c r="D2001" t="n">
         <v>-4.177681614337023</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.745666411328828</v>
+        <v>1.920279340559432</v>
       </c>
       <c r="F2001" t="n">
         <v>-0.1322400234161334</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.337751467327704</v>
+        <v>3.512364396558308</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.492721522075959</v>
+        <v>3.493315108889005</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.427101635022126</v>
+        <v>3.60171456425273</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.155060347465744</v>
+        <v>-4.072631074640598</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.764721071722081</v>
+        <v>1.972305710082743</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.004807952489195577</v>
+        <v>0.1781579322498953</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.429986406515643</v>
+        <v>3.708609323602667</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.1%</t>
+          <t>459.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-568.8%</t>
+          <t>-578.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-259.7%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>120.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.0%</t>
+          <t>-200.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-206.2%</t>
+          <t>-223.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-163.2%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-103.1%</t>
         </is>
       </c>
     </row>
@@ -43868,19 +43868,19 @@
         <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.330701626026427</v>
+        <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
         <v>-0.1508189717609766</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.270017613008289</v>
+        <v>3.095404683777685</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.30545252455241</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.309448007650164</v>
+        <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
         <v>-0.4080130064690334</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.145886380748803</v>
+        <v>2.971273451518199</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.129882485351313</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.310465616780634</v>
+        <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
         <v>-0.4737803965184454</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.120597033859509</v>
+        <v>2.945984104628904</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.130900094481784</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.30109364876839</v>
+        <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
         <v>-0.67902507357569</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.029127195024366</v>
+        <v>2.854514265793762</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.121528126469539</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.291176374723628</v>
+        <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
         <v>-0.7607969740034417</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.986501160808504</v>
+        <v>2.8118882315779</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.12783219646846</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.29594169155733</v>
+        <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
         <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.964382834493455</v>
+        <v>2.789769905262851</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.132597513302162</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.29376648767657</v>
+        <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
         <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.879181316856051</v>
+        <v>2.704568387625446</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.005882838786436</v>
+        <v>3.831269909555831</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.291693379181634</v>
+        <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
         <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.710006598942379</v>
+        <v>2.535393669711775</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.753157316163396</v>
+        <v>3.578544386932792</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.291559595780555</v>
+        <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
         <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.593820148899128</v>
+        <v>2.419207219668524</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.767472609606426</v>
+        <v>3.592859680375822</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.296451740334481</v>
+        <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
         <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.515510670111822</v>
+        <v>2.340897740881218</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.772364754160351</v>
+        <v>3.597751824929747</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.291533196672469</v>
+        <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
         <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.426027158094621</v>
+        <v>2.251414228864017</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.640598757965554</v>
+        <v>3.46598582873495</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.284617495978918</v>
+        <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
         <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.272683966543209</v>
+        <v>2.098071037312605</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.414041820985212</v>
+        <v>3.239428891754608</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.304955785717686</v>
+        <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
         <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.209625943701303</v>
+        <v>2.035013014470699</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.309285641852969</v>
+        <v>3.134672712622365</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.313054536126255</v>
+        <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
         <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.118844220203783</v>
+        <v>1.944231290973179</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.329476404360825</v>
+        <v>3.154863475130221</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.314160928169987</v>
+        <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
         <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.922996601037877</v>
+        <v>1.748383671807272</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.0351517795901</v>
+        <v>2.860538850359495</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.31270346698285</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
         <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.767466983478711</v>
+        <v>1.592854054248107</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.033694318402963</v>
+        <v>2.859081389172359</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.314472590437466</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
         <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.669287834927494</v>
+        <v>1.49467490569689</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.057221073755857</v>
+        <v>2.882608144525252</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.310578649093724</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
         <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.582789182828944</v>
+        <v>1.40817625359834</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.929420066279902</v>
+        <v>2.754807137049298</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.312351575793984</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
         <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.456824479497002</v>
+        <v>1.282211550266398</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.931192992980161</v>
+        <v>2.756580063749557</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.298684463261388</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
         <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.270435049704492</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.835675382582806</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.286969238263479</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
         <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.164842227053562</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.827761917922449</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.285549829919444</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
         <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.029157759817346</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.785583918285072</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.292037390153685</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
         <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8901948220914622</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.733138496399038</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.291291905159517</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
         <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7433983840417948</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.554606540825461</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.290053449174276</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.578724417184282</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.308214818531813</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.285238881645737</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
         <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4632794095294099</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.303400251003274</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.283232932254614</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
         <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2947167104234882</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.301394301612151</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.293491622923293</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
         <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.2072668408013394</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.31165299228083</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.289591188068988</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
         <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1212659982523303</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.307752557426526</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.287996108123989</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
         <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.05423896703357789</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.306157477481527</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.291775084053197</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
         <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.06064659376129322</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.268690571970408</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.287748779518794</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
         <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1393607816194171</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.264664267436005</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.28764667819721</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
         <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.292663438438054</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.264562166114421</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.29021819416864</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
         <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3628398388606375</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.15801180749483</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.29556849746669</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
         <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5013016645641879</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.16336211079288</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.303484517423868</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
         <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5135252699886994</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.141068692677524</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.306526268045637</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
         <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5495312303354889</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.085538876846455</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.309419824367209</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
         <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6056481092161738</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.999916780364641</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.314933021485851</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
         <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6818381822294768</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.92884661071489</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.319415575970287</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
         <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7070888182491069</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.846509450838522</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.334787277463708</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
         <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6623291840887058</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.905963051332413</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.349342498211225</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
         <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7178237302958062</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.815443621648003</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.342123333309629</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
         <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8188237328031982</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.808224456746407</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.335451142535653</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
         <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.867245815987753</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.738927427356564</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.336566932374209</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
         <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8872444883893271</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.682637925245682</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.339260661003324</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
         <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9349654771075282</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.700482627560642</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.343250996689725</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
         <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9101689358336023</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.704472963247043</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.341775769790983</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
         <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9683128994219921</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.702997736348301</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.356829179955855</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
         <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9334231514871862</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.747805653168073</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.343778046309172</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
         <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9413513279319594</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.70544105451605</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.353357119345381</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
         <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8414341938079866</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.740176132904557</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.35449626390144</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
         <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7904635867168914</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.741315277460616</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.357130038063548</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
         <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8089879277724981</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.746922259275791</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.362863742302184</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
         <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.7744009534187093</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.752655963514427</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.353126479908319</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
         <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7555916587687159</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.785738536686351</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.343242998595411</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
         <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7280915264875332</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.775855055373444</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.341408438096038</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
         <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6230293666395479</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.77402049487407</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.341108123122577</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
         <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5841668661424126</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.814511629816943</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.34177662926807</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
         <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5739169436065357</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.829552260548011</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.328516313106318</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
         <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.481553284439169</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.974727907379936</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839728</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.325729279446017</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
         <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.201508468697535</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.971940873719635</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.326072903333859</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
         <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1850911254632175</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.996395076627191</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.325439724554616</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
         <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1203643558667151</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.093801820411566</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.333364153392468</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
         <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.01904743813702314</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.241814982587178</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.330471943079509</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.03792690795302356</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.29466486701974</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.325839429826536</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.08620458415240551</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.369397637945299</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.328654490514173</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1513149778639389</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.46565569816878</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.341560831737831</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2638212385610301</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.478562039392439</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.213584902138613</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09360931305256948</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.287232115929358</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987906</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.262129244015699</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1346596940822171</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.332418852010365</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.142250321327531</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07395678795708927</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.224732478867332</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.133536335074053</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.0864306106052064</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.247800205966247</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.12657572297896</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.09688936121838942</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.240839593871154</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.141038077360103</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2082110729810758</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.255301948252297</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.135570197819298</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2460468482892795</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.249834068711492</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.133068291829875</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2928613962267086</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.321306843612347</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.1407692700672</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3090220540254114</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.341697341191739</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.136549978414251</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4023089391658394</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.337478049538789</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.138674292334267</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4451383811967737</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.347533804494263</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.131416367317969</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5378206137601054</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.340275879477965</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.135015490838618</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.611776574267727</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.343875002998614</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093391139299</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.148342996893172</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.693682665531266</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.460070386866645</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632784</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.147363474509469</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7224189694428986</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.503664603925946</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.152058275563786</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.75256806739079</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.546540850320624</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.133252534347581</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7783330299049536</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.52773510910442</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242298</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.134995610972459</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8762483052517753</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.673736483812213</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.138924924807279</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9090746463550734</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.677665797647033</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787997</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.139603508724619</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9309525591849686</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.711546136965536</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.136601579944613</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9714725845968526</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.70854420818553</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.138180616955227</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
         <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.061059940822271</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.794855152236932</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.15407479975705</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
         <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.130101199249405</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.810749335038755</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.155220644197352</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.179316277035507</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.883999029497757</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.165308746758792</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.247273237636842</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.980890419119039</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.151346238160218</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.209360798095191</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.931003014105849</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.173746731482784</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.26648109052936</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.953403507428416</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.173819132856196</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.26556560931805</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.951994084924744</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.184826055330898</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.249224457263148</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.968566426821175</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.175262763962789</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.946651115301141</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.196245893528585</v>
+        <v>1.021632964297981</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.959003135453067</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.999972329003176</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.977644274629847</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.00855819483749</v>
+        <v>0.8339452656068858</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.783712700493453</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.004539560994964</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.802170014837378</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.083315130746265</v>
+        <v>0.9087022015156609</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.788279932485241</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.980281589756171</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.913106267478627</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.014682658450973</v>
+        <v>0.8400697292203685</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.764021961246448</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.983412974976076</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.879442722006345</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.031279461859791</v>
+        <v>0.8566665326291869</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.787351473749723</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.993585361408209</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.819590102802621</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.065392895973413</v>
+        <v>0.8907799667428087</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.797523860181855</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.988531631982069</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.733346639776244</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.094836551757824</v>
+        <v>0.92022362252722</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.792470130755715</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.980307407426595</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.778653459175223</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.068489599442758</v>
+        <v>0.8938766702121537</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.759759808394703</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.980859280459696</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.807686563877525</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.057428230594939</v>
+        <v>0.8828153013643347</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.760311681427804</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.910131972351062</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.714876082426665</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.023825115066648</v>
+        <v>0.8492121858360442</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.745270662189685</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.912005448275663</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.759265551756092</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.007942803259478</v>
+        <v>0.8333298740288742</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.720510456516629</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.907081156787386</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.646594333519842</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.048086999065701</v>
+        <v>0.8734740698350971</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.783188895970103</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.912572452618053</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
         <v>-4.534217332337169</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.098529095369438</v>
+        <v>0.9239161661388335</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.78868019180077</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.924069654386592</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
         <v>-4.561997730238522</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.098914137977436</v>
+        <v>0.9243012087468316</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.783509154828497</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705329</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.762425374387245</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
         <v>-4.644999011263801</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9040693455679776</v>
+        <v>0.7294564163373733</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.610722344112846</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.882575035106451</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.753613089707132</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9807733749098506</v>
+        <v>0.8061604456792464</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.730872004832052</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190772</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.897088061208774</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.840211672688235</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9606469678197325</v>
+        <v>0.7860340385891282</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.745385030934375</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991343</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.894507502551142</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.801828010130084</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9734198741853617</v>
+        <v>0.7988069449547575</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.765834669811634</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753249</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.891236531396444</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
         <v>-4.624711680094918</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.04099543504473</v>
+        <v>0.8663825058141257</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.762563698656936</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793908</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.891919923158357</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
         <v>-4.669803924928464</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.023641928873225</v>
+        <v>0.8490289996426206</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.726109464517215</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011241</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.885706898464772</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
         <v>-4.490428503689696</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.089179072675146</v>
+        <v>0.914566143444542</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.813962494726061</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982235</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.866514353796362</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
         <v>-4.535442717210302</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.051980842598494</v>
+        <v>0.8773679133678893</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.776560612868888</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509544</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.872205916135307</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.802447227482737</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9508706008284653</v>
+        <v>0.7762576715978611</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.665634352382064</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.871409838031809</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.903645008919909</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9095954101500978</v>
+        <v>0.7349824809194936</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.623792986151374</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.869009799586125</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.871169422749137</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9201856061727234</v>
+        <v>0.7455726769421192</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.621392947705691</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378105</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.86553451879437</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.85213129504184</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9243255764638871</v>
+        <v>0.7497126472332829</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.583007500115219</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.043116387733051</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.883257926192458</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.08945679294232</v>
+        <v>0.9148438637117162</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.7605893690539</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067871</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.043949716719184</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.897124687526376</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084743417394887</v>
+        <v>0.9101304881642824</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.73870794799974</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789128</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.04995824711611</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.917381986055334</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.082649028380229</v>
+        <v>0.9080360991496252</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.744716478396666</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.129110894908132</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.769639015820331</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.220898864266252</v>
+        <v>1.046285935035648</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.924553540529617</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.131904516439613</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.871653698351553</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.182886612785245</v>
+        <v>1.008273683554641</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.927347162061098</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394738</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.132566864831272</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.865500992298768</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.186010043598017</v>
+        <v>1.011397114367413</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.931701134084427</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.131647341571382</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.88231029044927</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.178366801077926</v>
+        <v>1.003753871847322</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.920696031934237</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.197982895368203</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.820012291673148</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.269621554385196</v>
+        <v>1.095008625154592</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.987031585731057</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.906563767757601</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.61822209400799</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.058918505840658</v>
+        <v>0.8843055766100534</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.814423373421948</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.976854000079776</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.558331412365397</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.15316501081987</v>
+        <v>0.9785520815892659</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.92064801472968</v>
+        <v>2.746035085499075</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.99148173619582</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.656071956990371</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.128696529085924</v>
+        <v>0.9540835998553197</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.925742183965935</v>
+        <v>2.751129254735331</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489392</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.990017717020491</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.8324097171133</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.056697405861424</v>
+        <v>0.8820844766308196</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.818475508716849</v>
+        <v>2.643862579486245</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.98850933506042</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.755987670681374</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.085757842474123</v>
+        <v>0.911144913243519</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.816967126756778</v>
+        <v>2.642354197526173</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102497</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.988372202495856</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.711614539042805</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.103369962564987</v>
+        <v>0.9287570333343826</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.843453873175355</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863229</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.988372202495856</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.703660568748033</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.106551550682896</v>
+        <v>0.9319386214522916</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.843453873175355</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.994753959523661</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
         <v>-4.656004838186977</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.131995599935123</v>
+        <v>0.9573826707045185</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.878429068539793</v>
+        <v>2.703816139309189</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82270724432688</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.999646332898386</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.528320528392681</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.187961697227566</v>
+        <v>1.013348767996962</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.959932027791095</v>
+        <v>2.785319098560491</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.986401005374258</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.588987118795069</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.150449733542483</v>
+        <v>0.9758368043118786</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.897667710235848</v>
+        <v>2.723054781005243</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690032</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.990498707984886</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
         <v>-4.544148717186671</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.172482796796471</v>
+        <v>0.9978698675658666</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.904491472613398</v>
+        <v>2.729878543382794</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674316</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.994659647615964</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
         <v>-4.644907352943669</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.136340282124749</v>
+        <v>0.9617273528941452</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.23217096101282</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.855357071008273</v>
+        <v>2.680744141777669</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163225</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.000539250143802</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
         <v>-4.600704515857768</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.159901019486947</v>
+        <v>0.9852880902563426</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1879681239269196</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.88775837578765</v>
+        <v>2.713145446557046</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83822866302291</v>
+        <v>3.838228663022906</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.998949250613049</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
         <v>-4.637683543521211</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.143519408890817</v>
+        <v>0.9689064796602131</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.908352717331696</v>
+        <v>2.733739788101092</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042145</v>
+        <v>3.86392411404214</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.050197015796089</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
         <v>-4.657741622386052</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.186743942527921</v>
+        <v>1.012131013297316</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.959600482514736</v>
+        <v>2.784987553284132</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078287</v>
+        <v>3.865367715078283</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.048637720390342</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
         <v>-4.617810949208161</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.20115691639333</v>
+        <v>1.026543987162726</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1110635489576987</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.981999591015723</v>
+        <v>2.807386661785118</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232404</v>
+        <v>3.8645188762324</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.043585948628612</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
         <v>-4.566778856485634</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.216517981720611</v>
+        <v>1.041905052490007</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.06003145623517075</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.00756707488751</v>
+        <v>2.832954145656906</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84257639416212</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
-        <v>3.060773352721317</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
         <v>-4.501554675358428</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.259795058264198</v>
+        <v>1.085182129033594</v>
       </c>
       <c r="F1988" t="n">
         <v>0.005192724892034872</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.063888987656538</v>
+        <v>2.889276058425934</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639824</v>
+        <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
-        <v>3.056734325020597</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
         <v>-4.464127655287294</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.270726838591932</v>
+        <v>1.096113909361328</v>
       </c>
       <c r="F1989" t="n">
         <v>0.01044426292121653</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.063000882773327</v>
+        <v>2.888387953542723</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749928</v>
+        <v>3.845198842749924</v>
       </c>
       <c r="C1990" t="n">
-        <v>3.057991117351837</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
         <v>-4.484239311322002</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.263938968509289</v>
+        <v>1.089326039278685</v>
       </c>
       <c r="F1990" t="n">
         <v>0.02147160791863573</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.070874082103019</v>
+        <v>2.896261152872415</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393555</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.218548888373048</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
         <v>-4.430494496894798</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.445994665301382</v>
+        <v>1.271381736070778</v>
       </c>
       <c r="F1991" t="n">
         <v>0.03153491735909769</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.237469838788507</v>
+        <v>3.062856909557903</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714893</v>
+        <v>3.813251854714888</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.338661797590865</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
         <v>-4.406702928288656</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.575624201961656</v>
+        <v>1.401011272731052</v>
       </c>
       <c r="F1992" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.37185768917001</v>
+        <v>3.197244759939406</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756018</v>
+        <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.330369773604724</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
         <v>-4.380618844024847</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.577765811681038</v>
+        <v>1.403152882450434</v>
       </c>
       <c r="F1993" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.363565665183869</v>
+        <v>3.188952735953265</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654193</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.328562969188504</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
         <v>-4.3762845409678</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.577692728487637</v>
+        <v>1.403079799257033</v>
       </c>
       <c r="F1994" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.452748922759171</v>
+        <v>3.278135993528566</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717123</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.346117374915295</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.367392079574516</v>
+        <v>-4.379786240709725</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.598804118771741</v>
+        <v>1.419233525087054</v>
       </c>
       <c r="F1995" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.470303328485962</v>
+        <v>3.295690399255358</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702631</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.337972422319879</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.535868196544394</v>
+        <v>-4.548262357679603</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.523268719388374</v>
+        <v>1.343698125703687</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1790287535678631</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.445389674460597</v>
+        <v>3.270776745229993</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539974</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.408385083776723</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.838068667682811</v>
+        <v>-3.850462828818019</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.872801192389851</v>
+        <v>1.693230598705164</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.473593500295195</v>
+        <v>3.298980571064591</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389904</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.399049106273627</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.815347563999658</v>
+        <v>-3.827741725134867</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.872553656360017</v>
+        <v>1.692983062675329</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.464257522792099</v>
+        <v>3.289644593561495</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534942</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.557955232124796</v>
+        <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.955640163536851</v>
+        <v>-3.968034324672059</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.975342742396309</v>
+        <v>1.795772148711621</v>
       </c>
       <c r="F1999" t="n">
         <v>-0.03161190533974023</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.538988088920953</v>
+        <v>3.364375159690348</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77996275940168</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.595033054618443</v>
+        <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.110421170315106</v>
+        <v>-4.122815331450314</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.950508162178654</v>
+        <v>1.770937568493966</v>
       </c>
       <c r="F2000" t="n">
         <v>-0.06497957939421634</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.556045306981913</v>
+        <v>3.381432377751309</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557228</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.591708410607988</v>
+        <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.177681614337023</v>
+        <v>-4.190075775472232</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.920279340559432</v>
+        <v>1.740708746874744</v>
       </c>
       <c r="F2001" t="n">
         <v>-0.1322400234161334</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.512364396558308</v>
+        <v>3.337751467327704</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.493315108889005</v>
+        <v>3.760455993905388</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.60171456425273</v>
+        <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.072631074640598</v>
+        <v>-4.167604241433399</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.972305710082743</v>
+        <v>1.759703514135019</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1781579322498953</v>
+        <v>0.003465461399837777</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.708609323602667</v>
+        <v>3.429180911862028</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,17 +786,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>43.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.3%</t>
+          <t>459.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.3%</t>
+          <t>-570.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-259.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.3%</t>
+          <t>-179.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.6%</t>
+          <t>-206.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-163.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-103.1%</t>
+          <t>-92.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2002"/>
+  <dimension ref="A1:G2003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43868,19 +43868,19 @@
         <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.156088696795822</v>
+        <v>3.330701626026427</v>
       </c>
       <c r="D1840" t="n">
         <v>-0.1508189717609766</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.095404683777685</v>
+        <v>3.270017613008289</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.30545252455241</v>
       </c>
     </row>
     <row r="1841">
@@ -43891,19 +43891,19 @@
         <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.13483507841956</v>
+        <v>3.309448007650164</v>
       </c>
       <c r="D1841" t="n">
         <v>-0.4080130064690334</v>
       </c>
       <c r="E1841" t="n">
-        <v>2.971273451518199</v>
+        <v>3.145886380748803</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>4.129882485351313</v>
       </c>
     </row>
     <row r="1842">
@@ -43914,19 +43914,19 @@
         <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.13585268755003</v>
+        <v>3.310465616780634</v>
       </c>
       <c r="D1842" t="n">
         <v>-0.4737803965184454</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.945984104628904</v>
+        <v>3.120597033859509</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>4.130900094481784</v>
       </c>
     </row>
     <row r="1843">
@@ -43937,19 +43937,19 @@
         <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.126480719537785</v>
+        <v>3.30109364876839</v>
       </c>
       <c r="D1843" t="n">
         <v>-0.67902507357569</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.854514265793762</v>
+        <v>3.029127195024366</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>4.121528126469539</v>
       </c>
     </row>
     <row r="1844">
@@ -43960,19 +43960,19 @@
         <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.116563445493024</v>
+        <v>3.291176374723628</v>
       </c>
       <c r="D1844" t="n">
         <v>-0.7607969740034417</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.8118882315779</v>
+        <v>2.986501160808504</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>4.12783219646846</v>
       </c>
     </row>
     <row r="1845">
@@ -43983,19 +43983,19 @@
         <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.121328762326726</v>
+        <v>3.29594169155733</v>
       </c>
       <c r="D1845" t="n">
         <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.789769905262851</v>
+        <v>2.964382834493455</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>4.132597513302162</v>
       </c>
     </row>
     <row r="1846">
@@ -44006,19 +44006,19 @@
         <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.119153558445966</v>
+        <v>3.29376648767657</v>
       </c>
       <c r="D1846" t="n">
         <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.704568387625446</v>
+        <v>2.879181316856051</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.831269909555831</v>
+        <v>4.005882838786436</v>
       </c>
     </row>
     <row r="1847">
@@ -44029,19 +44029,19 @@
         <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.117080449951029</v>
+        <v>3.291693379181634</v>
       </c>
       <c r="D1847" t="n">
         <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.535393669711775</v>
+        <v>2.710006598942379</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.578544386932792</v>
+        <v>3.753157316163396</v>
       </c>
     </row>
     <row r="1848">
@@ -44052,19 +44052,19 @@
         <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.116946666549951</v>
+        <v>3.291559595780555</v>
       </c>
       <c r="D1848" t="n">
         <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.419207219668524</v>
+        <v>2.593820148899128</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.592859680375822</v>
+        <v>3.767472609606426</v>
       </c>
     </row>
     <row r="1849">
@@ -44075,19 +44075,19 @@
         <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.121838811103876</v>
+        <v>3.296451740334481</v>
       </c>
       <c r="D1849" t="n">
         <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.340897740881218</v>
+        <v>2.515510670111822</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.597751824929747</v>
+        <v>3.772364754160351</v>
       </c>
     </row>
     <row r="1850">
@@ -44098,19 +44098,19 @@
         <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.116920267441865</v>
+        <v>3.291533196672469</v>
       </c>
       <c r="D1850" t="n">
         <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251414228864017</v>
+        <v>2.426027158094621</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.46598582873495</v>
+        <v>3.640598757965554</v>
       </c>
     </row>
     <row r="1851">
@@ -44121,19 +44121,19 @@
         <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.110004566748314</v>
+        <v>3.284617495978918</v>
       </c>
       <c r="D1851" t="n">
         <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098071037312605</v>
+        <v>2.272683966543209</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239428891754608</v>
+        <v>3.414041820985212</v>
       </c>
     </row>
     <row r="1852">
@@ -44144,19 +44144,19 @@
         <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.130342856487082</v>
+        <v>3.304955785717686</v>
       </c>
       <c r="D1852" t="n">
         <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035013014470699</v>
+        <v>2.209625943701303</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.134672712622365</v>
+        <v>3.309285641852969</v>
       </c>
     </row>
     <row r="1853">
@@ -44167,19 +44167,19 @@
         <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.13844160689565</v>
+        <v>3.313054536126255</v>
       </c>
       <c r="D1853" t="n">
         <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944231290973179</v>
+        <v>2.118844220203783</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.154863475130221</v>
+        <v>3.329476404360825</v>
       </c>
     </row>
     <row r="1854">
@@ -44190,19 +44190,19 @@
         <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.139547998939383</v>
+        <v>3.314160928169987</v>
       </c>
       <c r="D1854" t="n">
         <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748383671807272</v>
+        <v>1.922996601037877</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.860538850359495</v>
+        <v>3.0351517795901</v>
       </c>
     </row>
     <row r="1855">
@@ -44213,19 +44213,19 @@
         <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138090537752246</v>
+        <v>3.31270346698285</v>
       </c>
       <c r="D1855" t="n">
         <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592854054248107</v>
+        <v>1.767466983478711</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859081389172359</v>
+        <v>3.033694318402963</v>
       </c>
     </row>
     <row r="1856">
@@ -44236,19 +44236,19 @@
         <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.314472590437466</v>
       </c>
       <c r="D1856" t="n">
         <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49467490569689</v>
+        <v>1.669287834927494</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882608144525252</v>
+        <v>3.057221073755857</v>
       </c>
     </row>
     <row r="1857">
@@ -44259,19 +44259,19 @@
         <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.310578649093724</v>
       </c>
       <c r="D1857" t="n">
         <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.40817625359834</v>
+        <v>1.582789182828944</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.754807137049298</v>
+        <v>2.929420066279902</v>
       </c>
     </row>
     <row r="1858">
@@ -44282,19 +44282,19 @@
         <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.312351575793984</v>
       </c>
       <c r="D1858" t="n">
         <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282211550266398</v>
+        <v>1.456824479497002</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.756580063749557</v>
+        <v>2.931192992980161</v>
       </c>
     </row>
     <row r="1859">
@@ -44305,19 +44305,19 @@
         <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.298684463261388</v>
       </c>
       <c r="D1859" t="n">
         <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.270435049704492</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.835675382582806</v>
       </c>
     </row>
     <row r="1860">
@@ -44328,19 +44328,19 @@
         <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.286969238263479</v>
       </c>
       <c r="D1860" t="n">
         <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>1.164842227053562</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.827761917922449</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.285549829919444</v>
       </c>
       <c r="D1861" t="n">
         <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>1.029157759817346</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.785583918285072</v>
       </c>
     </row>
     <row r="1862">
@@ -44374,19 +44374,19 @@
         <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.292037390153685</v>
       </c>
       <c r="D1862" t="n">
         <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.8901948220914622</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.733138496399038</v>
       </c>
     </row>
     <row r="1863">
@@ -44397,19 +44397,19 @@
         <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.291291905159517</v>
       </c>
       <c r="D1863" t="n">
         <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.7433983840417948</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.554606540825461</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.290053449174276</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.578724417184282</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.308214818531813</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.285238881645737</v>
       </c>
       <c r="D1865" t="n">
         <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.4632794095294099</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.303400251003274</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.283232932254614</v>
       </c>
       <c r="D1866" t="n">
         <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.2947167104234882</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.301394301612151</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.293491622923293</v>
       </c>
       <c r="D1867" t="n">
         <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.2072668408013394</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.31165299228083</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.289591188068988</v>
       </c>
       <c r="D1868" t="n">
         <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>0.1212659982523303</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.307752557426526</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.287996108123989</v>
       </c>
       <c r="D1869" t="n">
         <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>0.05423896703357789</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.306157477481527</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.291775084053197</v>
       </c>
       <c r="D1870" t="n">
         <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.06064659376129322</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.268690571970408</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.287748779518794</v>
       </c>
       <c r="D1871" t="n">
         <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.1393607816194171</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.264664267436005</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.28764667819721</v>
       </c>
       <c r="D1872" t="n">
         <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.292663438438054</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.264562166114421</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.29021819416864</v>
       </c>
       <c r="D1873" t="n">
         <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.3628398388606375</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.15801180749483</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.29556849746669</v>
       </c>
       <c r="D1874" t="n">
         <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.5013016645641879</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.16336211079288</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.303484517423868</v>
       </c>
       <c r="D1875" t="n">
         <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.5135252699886994</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.141068692677524</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.306526268045637</v>
       </c>
       <c r="D1876" t="n">
         <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.5495312303354889</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>2.085538876846455</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.309419824367209</v>
       </c>
       <c r="D1877" t="n">
         <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.6056481092161738</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.999916780364641</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.314933021485851</v>
       </c>
       <c r="D1878" t="n">
         <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.6818381822294768</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.92884661071489</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.319415575970287</v>
       </c>
       <c r="D1879" t="n">
         <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.7070888182491069</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.846509450838522</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.334787277463708</v>
       </c>
       <c r="D1880" t="n">
         <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.6623291840887058</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.905963051332413</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.349342498211225</v>
       </c>
       <c r="D1881" t="n">
         <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.7178237302958062</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.815443621648003</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.342123333309629</v>
       </c>
       <c r="D1882" t="n">
         <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.8188237328031982</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.808224456746407</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.335451142535653</v>
       </c>
       <c r="D1883" t="n">
         <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.867245815987753</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.738927427356564</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.336566932374209</v>
       </c>
       <c r="D1884" t="n">
         <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-0.8872444883893271</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.682637925245682</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.339260661003324</v>
       </c>
       <c r="D1885" t="n">
         <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-0.9349654771075282</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.700482627560642</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.343250996689725</v>
       </c>
       <c r="D1886" t="n">
         <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-0.9101689358336023</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.704472963247043</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.341775769790983</v>
       </c>
       <c r="D1887" t="n">
         <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-0.9683128994219921</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.702997736348301</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.356829179955855</v>
       </c>
       <c r="D1888" t="n">
         <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-0.9334231514871862</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.747805653168073</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.343778046309172</v>
       </c>
       <c r="D1889" t="n">
         <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-0.9413513279319594</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.70544105451605</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.353357119345381</v>
       </c>
       <c r="D1890" t="n">
         <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.8414341938079866</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.740176132904557</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.35449626390144</v>
       </c>
       <c r="D1891" t="n">
         <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.7904635867168914</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.741315277460616</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.357130038063548</v>
       </c>
       <c r="D1892" t="n">
         <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.8089879277724981</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.746922259275791</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.362863742302184</v>
       </c>
       <c r="D1893" t="n">
         <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.7744009534187093</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.752655963514427</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.353126479908319</v>
       </c>
       <c r="D1894" t="n">
         <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.7555916587687159</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.785738536686351</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.343242998595411</v>
       </c>
       <c r="D1895" t="n">
         <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.7280915264875332</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.775855055373444</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.341408438096038</v>
       </c>
       <c r="D1896" t="n">
         <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.6230293666395479</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.77402049487407</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.341108123122577</v>
       </c>
       <c r="D1897" t="n">
         <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.5841668661424126</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.814511629816943</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.34177662926807</v>
       </c>
       <c r="D1898" t="n">
         <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.5739169436065357</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.829552260548011</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.328516313106318</v>
       </c>
       <c r="D1899" t="n">
         <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.481553284439169</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.974727907379936</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.325729279446017</v>
       </c>
       <c r="D1900" t="n">
         <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.201508468697535</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.971940873719635</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.326072903333859</v>
       </c>
       <c r="D1901" t="n">
         <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.1850911254632175</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.996395076627191</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.325439724554616</v>
       </c>
       <c r="D1902" t="n">
         <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.1203643558667151</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>2.093801820411566</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.333364153392468</v>
       </c>
       <c r="D1903" t="n">
         <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.01904743813702314</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.241814982587178</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.330471943079509</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>0.03792690795302356</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.29466486701974</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.325839429826536</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>0.08620458415240551</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.369397637945299</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.328654490514173</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>0.1513149778639389</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.46565569816878</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.341560831737831</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.2638212385610301</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.478562039392439</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.213584902138613</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>0.09360931305256948</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.287232115929358</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.262129244015699</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>0.1346596940822171</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.332418852010365</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.142250321327531</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>0.07395678795708927</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.224732478867332</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.133536335074053</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>0.0864306106052064</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.247800205966247</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.12657572297896</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>0.09688936121838942</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.240839593871154</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.141038077360103</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.2082110729810758</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.255301948252297</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.135570197819298</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.2460468482892795</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.249834068711492</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.133068291829875</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.2928613962267086</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.321306843612347</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.1407692700672</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.3090220540254114</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.341697341191739</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.136549978414251</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.4023089391658394</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.337478049538789</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.138674292334267</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.4451383811967737</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.347533804494263</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.131416367317969</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.5378206137601054</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.340275879477965</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.135015490838618</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.611776574267727</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.343875002998614</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.148342996893172</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.693682665531266</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.460070386866645</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.147363474509469</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.7224189694428986</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.503664603925946</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.152058275563786</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.75256806739079</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.546540850320624</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.133252534347581</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.7783330299049536</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.52773510910442</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.134995610972459</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.8762483052517753</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.673736483812213</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.138924924807279</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.9090746463550734</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.677665797647033</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.139603508724619</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.9309525591849686</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.711546136965536</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.136601579944613</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.9714725845968526</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.70854420818553</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.138180616955227</v>
       </c>
       <c r="D1929" t="n">
         <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>1.061059940822271</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.794855152236932</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.15407479975705</v>
       </c>
       <c r="D1930" t="n">
         <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>1.130101199249405</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.810749335038755</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.155220644197352</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.179316277035507</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.883999029497757</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.165308746758792</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.247273237636842</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.980890419119039</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.151346238160218</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.209360798095191</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.931003014105849</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.173746731482784</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.26648109052936</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.953403507428416</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.173819132856196</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.26556560931805</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.951994084924744</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.184826055330898</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.249224457263148</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.968566426821175</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.175262763962789</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.946651115301141</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.021632964297981</v>
+        <v>1.196245893528585</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.959003135453067</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.999972329003176</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.977644274629847</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8339452656068858</v>
+        <v>1.00855819483749</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.783712700493453</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>3.004539560994964</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.802170014837378</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9087022015156609</v>
+        <v>1.083315130746265</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.788279932485241</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.980281589756171</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.913106267478627</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8400697292203685</v>
+        <v>1.014682658450973</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.764021961246448</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.983412974976076</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.879442722006345</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8566665326291869</v>
+        <v>1.031279461859791</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.787351473749723</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.993585361408209</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.819590102802621</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8907799667428087</v>
+        <v>1.065392895973413</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.797523860181855</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.988531631982069</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.733346639776244</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.92022362252722</v>
+        <v>1.094836551757824</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.792470130755715</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.980307407426595</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.778653459175223</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8938766702121537</v>
+        <v>1.068489599442758</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.759759808394703</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.980859280459696</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.807686563877525</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8828153013643347</v>
+        <v>1.057428230594939</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.760311681427804</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.910131972351062</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.714876082426665</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8492121858360442</v>
+        <v>1.023825115066648</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.745270662189685</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.912005448275663</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.759265551756092</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8333298740288742</v>
+        <v>1.007942803259478</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.720510456516629</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.907081156787386</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.646594333519842</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8734740698350971</v>
+        <v>1.048086999065701</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.783188895970103</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.912572452618053</v>
       </c>
       <c r="D1949" t="n">
         <v>-4.534217332337169</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9239161661388335</v>
+        <v>1.098529095369438</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.78868019180077</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.924069654386592</v>
       </c>
       <c r="D1950" t="n">
         <v>-4.561997730238522</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9243012087468316</v>
+        <v>1.098914137977436</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.783509154828497</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.762425374387245</v>
       </c>
       <c r="D1951" t="n">
         <v>-4.644999011263801</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7294564163373733</v>
+        <v>0.9040693455679776</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.610722344112846</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.882575035106451</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.753613089707132</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8061604456792464</v>
+        <v>0.9807733749098506</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.730872004832052</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.897088061208774</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.840211672688235</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7860340385891282</v>
+        <v>0.9606469678197325</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.745385030934375</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.894507502551142</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.801828010130084</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7988069449547575</v>
+        <v>0.9734198741853617</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.765834669811634</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.891236531396444</v>
       </c>
       <c r="D1955" t="n">
         <v>-4.624711680094918</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8663825058141257</v>
+        <v>1.04099543504473</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.762563698656936</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.891919923158357</v>
       </c>
       <c r="D1956" t="n">
         <v>-4.669803924928464</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8490289996426206</v>
+        <v>1.023641928873225</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.726109464517215</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.885706898464772</v>
       </c>
       <c r="D1957" t="n">
         <v>-4.490428503689696</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.914566143444542</v>
+        <v>1.089179072675146</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.813962494726061</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.866514353796362</v>
       </c>
       <c r="D1958" t="n">
         <v>-4.535442717210302</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8773679133678893</v>
+        <v>1.051980842598494</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.776560612868888</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.872205916135307</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.802447227482737</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7762576715978611</v>
+        <v>0.9508706008284653</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.665634352382064</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.871409838031809</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.903645008919909</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7349824809194936</v>
+        <v>0.9095954101500978</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.623792986151374</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.869009799586125</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.871169422749137</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7455726769421192</v>
+        <v>0.9201856061727234</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.621392947705691</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.86553451879437</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.85213129504184</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7497126472332829</v>
+        <v>0.9243255764638871</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.583007500115219</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>3.043116387733051</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.883257926192458</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9148438637117162</v>
+        <v>1.08945679294232</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.7605893690539</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>3.043949716719184</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.897124687526376</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9101304881642824</v>
+        <v>1.084743417394887</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.73870794799974</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>3.04995824711611</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.917381986055334</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9080360991496252</v>
+        <v>1.082649028380229</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.744716478396666</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.129110894908132</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.769639015820331</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.046285935035648</v>
+        <v>1.220898864266252</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.924553540529617</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.131904516439613</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.871653698351553</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.008273683554641</v>
+        <v>1.182886612785245</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.927347162061098</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.132566864831272</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.865500992298768</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011397114367413</v>
+        <v>1.186010043598017</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.931701134084427</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.131647341571382</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.88231029044927</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.003753871847322</v>
+        <v>1.178366801077926</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.920696031934237</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.197982895368203</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.820012291673148</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.095008625154592</v>
+        <v>1.269621554385196</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.987031585731057</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.906563767757601</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.61822209400799</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8843055766100534</v>
+        <v>1.058918505840658</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.814423373421948</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.976854000079776</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.558331412365397</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9785520815892659</v>
+        <v>1.15316501081987</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746035085499075</v>
+        <v>2.92064801472968</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.99148173619582</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.656071956990371</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9540835998553197</v>
+        <v>1.128696529085924</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751129254735331</v>
+        <v>2.925742183965935</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.990017717020491</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.8324097171133</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8820844766308196</v>
+        <v>1.056697405861424</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.643862579486245</v>
+        <v>2.818475508716849</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.98850933506042</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.755987670681374</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.911144913243519</v>
+        <v>1.085757842474123</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642354197526173</v>
+        <v>2.816967126756778</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.988372202495856</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.711614539042805</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9287570333343826</v>
+        <v>1.103369962564987</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668840943944751</v>
+        <v>2.843453873175355</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.988372202495856</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.703660568748033</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9319386214522916</v>
+        <v>1.106551550682896</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668840943944751</v>
+        <v>2.843453873175355</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.994753959523661</v>
       </c>
       <c r="D1978" t="n">
         <v>-4.656004838186977</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9573826707045185</v>
+        <v>1.131995599935123</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.703816139309189</v>
+        <v>2.878429068539793</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.999646332898386</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.528320528392681</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.013348767996962</v>
+        <v>1.187961697227566</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785319098560491</v>
+        <v>2.959932027791095</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.986401005374258</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.588987118795069</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9758368043118786</v>
+        <v>1.150449733542483</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.723054781005243</v>
+        <v>2.897667710235848</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.990498707984886</v>
       </c>
       <c r="D1981" t="n">
         <v>-4.544148717186671</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9978698675658666</v>
+        <v>1.172482796796471</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.729878543382794</v>
+        <v>2.904491472613398</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.994659647615964</v>
       </c>
       <c r="D1982" t="n">
         <v>-4.644907352943669</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9617273528941452</v>
+        <v>1.136340282124749</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.23217096101282</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.680744141777669</v>
+        <v>2.855357071008273</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>3.000539250143802</v>
       </c>
       <c r="D1983" t="n">
         <v>-4.600704515857768</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9852880902563426</v>
+        <v>1.159901019486947</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1879681239269196</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713145446557046</v>
+        <v>2.88775837578765</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022906</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.998949250613049</v>
       </c>
       <c r="D1984" t="n">
         <v>-4.637683543521211</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9689064796602131</v>
+        <v>1.143519408890817</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.733739788101092</v>
+        <v>2.908352717331696</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.86392411404214</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>3.050197015796089</v>
       </c>
       <c r="D1985" t="n">
         <v>-4.657741622386052</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.012131013297316</v>
+        <v>1.186743942527921</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.784987553284132</v>
+        <v>2.959600482514736</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078283</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>3.048637720390342</v>
       </c>
       <c r="D1986" t="n">
         <v>-4.617810949208161</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.026543987162726</v>
+        <v>1.20115691639333</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1110635489576987</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.807386661785118</v>
+        <v>2.981999591015723</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.8645188762324</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>3.043585948628612</v>
       </c>
       <c r="D1987" t="n">
         <v>-4.566778856485634</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.041905052490007</v>
+        <v>1.216517981720611</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.06003145623517075</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.832954145656906</v>
+        <v>3.00756707488751</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>3.060773352721317</v>
       </c>
       <c r="D1988" t="n">
         <v>-4.501554675358428</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.085182129033594</v>
+        <v>1.259795058264198</v>
       </c>
       <c r="F1988" t="n">
         <v>0.005192724892034872</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.889276058425934</v>
+        <v>3.063888987656538</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>3.056734325020597</v>
       </c>
       <c r="D1989" t="n">
         <v>-4.464127655287294</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.096113909361328</v>
+        <v>1.270726838591932</v>
       </c>
       <c r="F1989" t="n">
         <v>0.01044426292121653</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.888387953542723</v>
+        <v>3.063000882773327</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749924</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>3.057991117351837</v>
       </c>
       <c r="D1990" t="n">
         <v>-4.484239311322002</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.089326039278685</v>
+        <v>1.263938968509289</v>
       </c>
       <c r="F1990" t="n">
         <v>0.02147160791863573</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.896261152872415</v>
+        <v>3.070874082103019</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.218548888373048</v>
       </c>
       <c r="D1991" t="n">
         <v>-4.430494496894798</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.271381736070778</v>
+        <v>1.445994665301382</v>
       </c>
       <c r="F1991" t="n">
         <v>0.03153491735909769</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.062856909557903</v>
+        <v>3.237469838788507</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714888</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.338661797590865</v>
       </c>
       <c r="D1992" t="n">
         <v>-4.406702928288656</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.401011272731052</v>
+        <v>1.575624201961656</v>
       </c>
       <c r="F1992" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197244759939406</v>
+        <v>3.37185768917001</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.330369773604724</v>
       </c>
       <c r="D1993" t="n">
         <v>-4.380618844024847</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.403152882450434</v>
+        <v>1.577765811681038</v>
       </c>
       <c r="F1993" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.188952735953265</v>
+        <v>3.363565665183869</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.328562969188504</v>
       </c>
       <c r="D1994" t="n">
         <v>-4.3762845409678</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.403079799257033</v>
+        <v>1.577692728487637</v>
       </c>
       <c r="F1994" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278135993528566</v>
+        <v>3.452748922759171</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.346117374915295</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.379786240709725</v>
+        <v>-4.37981086046535</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.419233525087054</v>
+        <v>1.593836606415408</v>
       </c>
       <c r="F1995" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.295690399255358</v>
+        <v>3.470303328485962</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.337972422319879</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.548262357679603</v>
+        <v>-4.548286977435227</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.343698125703687</v>
+        <v>1.518301207032041</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1790287535678631</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.270776745229993</v>
+        <v>3.445389674460597</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.408385083776723</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.850462828818019</v>
+        <v>-3.850487448573644</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.693230598705164</v>
+        <v>1.867833680033518</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.298980571064591</v>
+        <v>3.473593500295195</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.399049106273627</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.827741725134867</v>
+        <v>-3.827766344890491</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.692983062675329</v>
+        <v>1.867586144003684</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.289644593561495</v>
+        <v>3.464257522792099</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.383342302894192</v>
+        <v>3.557955232124796</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.968034324672059</v>
+        <v>-3.968058944427684</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.795772148711621</v>
+        <v>1.970375230039976</v>
       </c>
       <c r="F1999" t="n">
         <v>-0.03161190533974023</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.364375159690348</v>
+        <v>3.538988088920953</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.420420125387839</v>
+        <v>3.595033054618443</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.122815331450314</v>
+        <v>-4.122839951205939</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.770937568493966</v>
+        <v>1.94554064982232</v>
       </c>
       <c r="F2000" t="n">
         <v>-0.06497957939421634</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.381432377751309</v>
+        <v>3.556045306981913</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.417095481377384</v>
+        <v>3.591708410607988</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.190075775472232</v>
+        <v>-4.190100395227856</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.740708746874744</v>
+        <v>1.915311828203099</v>
       </c>
       <c r="F2001" t="n">
         <v>-0.1322400234161334</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.337751467327704</v>
+        <v>3.512364396558308</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,45 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.760455993905388</v>
+        <v>3.766702530088372</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.427101635022126</v>
+        <v>3.60171456425273</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.167604241433399</v>
+        <v>-4.085343975141726</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.759703514135019</v>
+        <v>1.967220549882292</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.1778638126396005</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.429180911862028</v>
+        <v>3.70843285183649</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="2" t="n">
+        <v>45465</v>
+      </c>
+      <c r="B2003" t="n">
+        <v>3.760438642162438</v>
+      </c>
+      <c r="C2003" t="n">
+        <v>3.547379366678197</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>-4.085343975141726</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>1.967220549882292</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>0.1778638126396005</v>
+      </c>
+      <c r="G2003" t="n">
+        <v>3.540443163664565</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,42 +834,42 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>62.4%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>30.4%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>29.9%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.5%</t>
+          <t>454.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.1%</t>
+          <t>-588.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-259.7%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>120.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.5%</t>
+          <t>-204.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>158.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-170.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-206.2%</t>
+          <t>-226.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-163.2%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-92.0%</t>
+          <t>-118.3%</t>
         </is>
       </c>
     </row>
@@ -43868,19 +43868,19 @@
         <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.330701626026427</v>
+        <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
         <v>-0.1508189717609766</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.270017613008289</v>
+        <v>3.095404683777685</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.30545252455241</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43891,19 +43891,19 @@
         <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.309448007650164</v>
+        <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
         <v>-0.4080130064690334</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.145886380748803</v>
+        <v>2.971273451518199</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.129882485351313</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43914,19 +43914,19 @@
         <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.310465616780634</v>
+        <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
         <v>-0.4737803965184454</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.120597033859509</v>
+        <v>2.945984104628904</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.130900094481784</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43937,19 +43937,19 @@
         <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.30109364876839</v>
+        <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
         <v>-0.67902507357569</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.029127195024366</v>
+        <v>2.854514265793762</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.121528126469539</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43960,19 +43960,19 @@
         <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.291176374723628</v>
+        <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
         <v>-0.7607969740034417</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.986501160808504</v>
+        <v>2.8118882315779</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.12783219646846</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43983,19 +43983,19 @@
         <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.29594169155733</v>
+        <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
         <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.964382834493455</v>
+        <v>2.789769905262851</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.132597513302162</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44006,19 +44006,19 @@
         <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.29376648767657</v>
+        <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
         <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.879181316856051</v>
+        <v>2.704568387625446</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.005882838786436</v>
+        <v>3.831269909555831</v>
       </c>
     </row>
     <row r="1847">
@@ -44029,19 +44029,19 @@
         <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.291693379181634</v>
+        <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
         <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.710006598942379</v>
+        <v>2.535393669711775</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.753157316163396</v>
+        <v>3.578544386932792</v>
       </c>
     </row>
     <row r="1848">
@@ -44052,19 +44052,19 @@
         <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.291559595780555</v>
+        <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
         <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.593820148899128</v>
+        <v>2.419207219668524</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.767472609606426</v>
+        <v>3.592859680375822</v>
       </c>
     </row>
     <row r="1849">
@@ -44075,19 +44075,19 @@
         <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.296451740334481</v>
+        <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
         <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.515510670111822</v>
+        <v>2.340897740881218</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.772364754160351</v>
+        <v>3.597751824929747</v>
       </c>
     </row>
     <row r="1850">
@@ -44098,19 +44098,19 @@
         <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.291533196672469</v>
+        <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
         <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.426027158094621</v>
+        <v>2.251414228864017</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.640598757965554</v>
+        <v>3.46598582873495</v>
       </c>
     </row>
     <row r="1851">
@@ -44121,19 +44121,19 @@
         <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.284617495978918</v>
+        <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
         <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.272683966543209</v>
+        <v>2.098071037312605</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.414041820985212</v>
+        <v>3.239428891754608</v>
       </c>
     </row>
     <row r="1852">
@@ -44144,19 +44144,19 @@
         <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.304955785717686</v>
+        <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
         <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.209625943701303</v>
+        <v>2.035013014470699</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.309285641852969</v>
+        <v>3.134672712622365</v>
       </c>
     </row>
     <row r="1853">
@@ -44167,19 +44167,19 @@
         <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.313054536126255</v>
+        <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
         <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.118844220203783</v>
+        <v>1.944231290973179</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.329476404360825</v>
+        <v>3.154863475130221</v>
       </c>
     </row>
     <row r="1854">
@@ -44190,19 +44190,19 @@
         <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.314160928169987</v>
+        <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
         <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.922996601037877</v>
+        <v>1.748383671807272</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.0351517795901</v>
+        <v>2.860538850359495</v>
       </c>
     </row>
     <row r="1855">
@@ -44213,19 +44213,19 @@
         <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.31270346698285</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
         <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.767466983478711</v>
+        <v>1.592854054248107</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.033694318402963</v>
+        <v>2.859081389172359</v>
       </c>
     </row>
     <row r="1856">
@@ -44236,19 +44236,19 @@
         <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.314472590437466</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
         <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.669287834927494</v>
+        <v>1.49467490569689</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.057221073755857</v>
+        <v>2.882608144525252</v>
       </c>
     </row>
     <row r="1857">
@@ -44259,19 +44259,19 @@
         <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.310578649093724</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
         <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.582789182828944</v>
+        <v>1.40817625359834</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.929420066279902</v>
+        <v>2.754807137049298</v>
       </c>
     </row>
     <row r="1858">
@@ -44282,19 +44282,19 @@
         <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.312351575793984</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
         <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.456824479497002</v>
+        <v>1.282211550266398</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.931192992980161</v>
+        <v>2.756580063749557</v>
       </c>
     </row>
     <row r="1859">
@@ -44305,19 +44305,19 @@
         <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.298684463261388</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
         <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.270435049704492</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.835675382582806</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44328,19 +44328,19 @@
         <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.286969238263479</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
         <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.164842227053562</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.827761917922449</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.285549829919444</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
         <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.029157759817346</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.785583918285072</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44374,19 +44374,19 @@
         <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.292037390153685</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
         <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8901948220914622</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.733138496399038</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44397,19 +44397,19 @@
         <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.291291905159517</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
         <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7433983840417948</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.554606540825461</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.290053449174276</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.578724417184282</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.308214818531813</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.285238881645737</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
         <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4632794095294099</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.303400251003274</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.283232932254614</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
         <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2947167104234882</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.301394301612151</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.293491622923293</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
         <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.2072668408013394</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.31165299228083</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.289591188068988</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
         <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1212659982523303</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.307752557426526</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.287996108123989</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
         <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.05423896703357789</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.306157477481527</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.291775084053197</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
         <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.06064659376129322</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.268690571970408</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.287748779518794</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
         <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1393607816194171</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.264664267436005</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.28764667819721</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
         <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.292663438438054</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.264562166114421</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.29021819416864</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
         <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3628398388606375</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.15801180749483</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.29556849746669</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
         <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5013016645641879</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.16336211079288</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.303484517423868</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
         <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5135252699886994</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.141068692677524</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.306526268045637</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
         <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5495312303354889</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.085538876846455</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.309419824367209</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
         <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6056481092161738</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.999916780364641</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.314933021485851</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
         <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6818381822294768</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.92884661071489</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.319415575970287</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
         <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7070888182491069</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.846509450838522</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.334787277463708</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
         <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6623291840887058</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.905963051332413</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.349342498211225</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
         <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7178237302958062</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.815443621648003</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.342123333309629</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
         <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8188237328031982</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.808224456746407</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.335451142535653</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
         <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.867245815987753</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.738927427356564</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.336566932374209</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
         <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8872444883893271</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.682637925245682</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.339260661003324</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
         <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9349654771075282</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.700482627560642</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.343250996689725</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
         <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9101689358336023</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.704472963247043</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.341775769790983</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
         <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9683128994219921</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.702997736348301</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.356829179955855</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
         <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9334231514871862</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.747805653168073</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.343778046309172</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
         <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9413513279319594</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.70544105451605</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.353357119345381</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
         <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8414341938079866</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.740176132904557</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.35449626390144</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
         <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7904635867168914</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.741315277460616</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.357130038063548</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
         <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8089879277724981</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.746922259275791</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.362863742302184</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
         <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.7744009534187093</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.752655963514427</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.353126479908319</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
         <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7555916587687159</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.785738536686351</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.343242998595411</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
         <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7280915264875332</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.775855055373444</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.341408438096038</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
         <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6230293666395479</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.77402049487407</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.341108123122577</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
         <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5841668661424126</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.814511629816943</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.34177662926807</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
         <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5739169436065357</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.829552260548011</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.328516313106318</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
         <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.481553284439169</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.974727907379936</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.325729279446017</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
         <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.201508468697535</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.971940873719635</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.326072903333859</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
         <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1850911254632175</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.996395076627191</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.325439724554616</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
         <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1203643558667151</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.093801820411566</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.333364153392468</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
         <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.01904743813702314</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.241814982587178</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.330471943079509</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.03792690795302356</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.29466486701974</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.325839429826536</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.08620458415240551</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.369397637945299</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.328654490514173</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1513149778639389</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.46565569816878</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.341560831737831</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2638212385610301</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.478562039392439</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.213584902138613</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09360931305256948</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.287232115929358</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.262129244015699</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1346596940822171</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.332418852010365</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.142250321327531</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07395678795708927</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.224732478867332</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.133536335074053</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.0864306106052064</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.247800205966247</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.12657572297896</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.09688936121838942</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.240839593871154</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.141038077360103</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2082110729810758</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.255301948252297</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.135570197819298</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2460468482892795</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.249834068711492</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.133068291829875</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2928613962267086</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.321306843612347</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.1407692700672</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3090220540254114</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.341697341191739</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.136549978414251</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4023089391658394</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.337478049538789</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.138674292334267</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4451383811967737</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.347533804494263</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.131416367317969</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5378206137601054</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.340275879477965</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.135015490838618</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.611776574267727</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.343875002998614</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.148342996893172</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.693682665531266</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.460070386866645</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.147363474509469</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7224189694428986</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.503664603925946</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.152058275563786</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.75256806739079</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.546540850320624</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.133252534347581</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7783330299049536</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.52773510910442</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.134995610972459</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8762483052517753</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.673736483812213</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.138924924807279</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9090746463550734</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.677665797647033</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.139603508724619</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9309525591849686</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.711546136965536</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.136601579944613</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9714725845968526</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.70854420818553</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.138180616955227</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
         <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.061059940822271</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.794855152236932</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.15407479975705</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
         <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.130101199249405</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.810749335038755</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.155220644197352</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.179316277035507</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.883999029497757</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.165308746758792</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.247273237636842</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.980890419119039</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.151346238160218</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.209360798095191</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.931003014105849</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.173746731482784</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.825431782556716</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.26648109052936</v>
+        <v>1.068604664915746</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.953403507428416</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.173819132856196</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.827901489018522</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.26556560931805</v>
+        <v>1.067689183704435</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.951994084924744</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.184826055330898</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.896271675342533</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.249224457263148</v>
+        <v>1.051348031649533</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.968566426821175</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.175262763962789</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.946651115301141</v>
+        <v>-5.004809856258666</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.196245893528585</v>
+        <v>0.9983694679149711</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.959003135453067</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.999972329003176</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.977644274629847</v>
+        <v>-5.035803015587372</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.00855819483749</v>
+        <v>0.8106817692238755</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.783712700493453</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.004539560994964</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.802170014837378</v>
+        <v>-4.860328755794903</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.083315130746265</v>
+        <v>0.8854387051326509</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.788279932485241</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.980281589756171</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.913106267478627</v>
+        <v>-4.971265008436152</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.014682658450973</v>
+        <v>0.8168062328373584</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.764021961246448</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.983412974976076</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.879442722006345</v>
+        <v>-4.93760146296387</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.031279461859791</v>
+        <v>0.8334030362461768</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.787351473749723</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.993585361408209</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.819590102802621</v>
+        <v>-4.877748843760147</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.065392895973413</v>
+        <v>0.8675164703597984</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.797523860181855</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.988531631982069</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.733346639776244</v>
+        <v>-4.791505380733769</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.094836551757824</v>
+        <v>0.8969601261442099</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.792470130755715</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.980307407426595</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.778653459175223</v>
+        <v>-4.836812200132749</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.068489599442758</v>
+        <v>0.8706131738291436</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.759759808394703</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.980859280459696</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.807686563877525</v>
+        <v>-4.86584530483505</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.057428230594939</v>
+        <v>0.8595518049813247</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.760311681427804</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.910131972351062</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.714876082426665</v>
+        <v>-4.77303482338419</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.023825115066648</v>
+        <v>0.8259486894530341</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.745270662189685</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.912005448275663</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.759265551756092</v>
+        <v>-4.817424292713618</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.007942803259478</v>
+        <v>0.8100663776458639</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.720510456516629</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.907081156787386</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.646594333519842</v>
+        <v>-4.796591975741188</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.048086999065701</v>
+        <v>0.8134750129465589</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.2983260026259584</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.783188895970103</v>
+        <v>2.553472625981207</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.912572452618053</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.534217332337169</v>
+        <v>-4.684214974558515</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.098529095369438</v>
+        <v>0.8639171092502953</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.2983260026259584</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.78868019180077</v>
+        <v>2.558963921811874</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.924069654386592</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.561997730238522</v>
+        <v>-4.711995372459867</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.098914137977436</v>
+        <v>0.8643021518582934</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.3261064005273114</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.783509154828497</v>
+        <v>2.553792884839601</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.762425374387245</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.644999011263801</v>
+        <v>-4.794996653485146</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9040693455679776</v>
+        <v>0.6694573594488351</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.3446772850544852</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.610722344112846</v>
+        <v>2.38100607412395</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.882575035106451</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.753613089707132</v>
+        <v>-4.903610731928477</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9807733749098506</v>
+        <v>0.7461613887907084</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.3446772850544852</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.730872004832052</v>
+        <v>2.501155734843155</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.897088061208774</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.840211672688235</v>
+        <v>-4.99020931490958</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9606469678197325</v>
+        <v>0.72603498170059</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.3446772850544852</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.745385030934375</v>
+        <v>2.515668760945478</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.894507502551142</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.801828010130084</v>
+        <v>-4.951825652351429</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9734198741853617</v>
+        <v>0.7388078880662192</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.306293622496334</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.765834669811634</v>
+        <v>2.536118399822738</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.891236531396444</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.624711680094918</v>
+        <v>-4.774709322316263</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.04099543504473</v>
+        <v>0.8063834489255877</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.306293622496334</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.762563698656936</v>
+        <v>2.53284742866804</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.891919923158357</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.669803924928464</v>
+        <v>-4.819801567149809</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.023641928873225</v>
+        <v>0.7890299427540823</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.3681896656657238</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.726109464517215</v>
+        <v>2.496393194528319</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.885706898464772</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.490428503689696</v>
+        <v>-4.640426145911041</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.089179072675146</v>
+        <v>0.8545670865560038</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.2114129074950051</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.813962494726061</v>
+        <v>2.584246224737165</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.866514353796362</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.535442717210302</v>
+        <v>-4.685440359431647</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.051980842598494</v>
+        <v>0.8173688564793513</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.2417618028096097</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.776560612868888</v>
+        <v>2.546844342879992</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.872205916135307</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.802447227482737</v>
+        <v>-4.952444869704082</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9508706008284653</v>
+        <v>0.7162586147093231</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.4361248408525583</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.665634352382064</v>
+        <v>2.435918082393168</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.871409838031809</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.903645008919909</v>
+        <v>-5.053642651141255</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9095954101500978</v>
+        <v>0.6749834240309553</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.5045336543978776</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.623792986151374</v>
+        <v>2.394076716162478</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.869009799586125</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.871169422749137</v>
+        <v>-5.021167064970482</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9201856061727234</v>
+        <v>0.6855736200535811</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.5045336543978776</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.621392947705691</v>
+        <v>2.391676677716795</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.86553451879437</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.85213129504184</v>
+        <v>-5.002128937263185</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9243255764638871</v>
+        <v>0.6897135903447449</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.5627172657290722</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.583007500115219</v>
+        <v>2.353291230126323</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.043116387733051</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.883257926192458</v>
+        <v>-4.994262181648599</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.08945679294232</v>
+        <v>0.8704421615292597</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.5627172657290722</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.7605893690539</v>
+        <v>2.530873099065003</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.043949716719184</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.897124687526376</v>
+        <v>-5.008128942982517</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084743417394887</v>
+        <v>0.8657287859818261</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.6005751824628951</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.73870794799974</v>
+        <v>2.508991678010843</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.04995824711611</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.917381986055334</v>
+        <v>-5.028386241511475</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.082649028380229</v>
+        <v>0.8636343969671687</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.6005751824628951</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.744716478396666</v>
+        <v>2.515000208407769</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.129110894908132</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.769639015820331</v>
+        <v>-4.880643271276472</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.220898864266252</v>
+        <v>1.001884232853192</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.4327678252280119</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.924553540529617</v>
+        <v>2.694837270540721</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.131904516439613</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.871653698351553</v>
+        <v>-4.982657953807694</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.182886612785245</v>
+        <v>0.9638719813721843</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.4327678252280119</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.927347162061098</v>
+        <v>2.697630892072202</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.132566864831272</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.865500992298768</v>
+        <v>-4.976505247754909</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.186010043598017</v>
+        <v>0.9669954121849564</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.4266151191752277</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.931701134084427</v>
+        <v>2.701984864095531</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.131647341571382</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.88231029044927</v>
+        <v>-4.993314545905411</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.178366801077926</v>
+        <v>0.9593521696648659</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.4434244173257293</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.920696031934237</v>
+        <v>2.69097976194534</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.197982895368203</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.820012291673148</v>
+        <v>-4.931016547129289</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.269621554385196</v>
+        <v>1.050606922972136</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3811264185496073</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.987031585731057</v>
+        <v>2.794694115007835</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.906563767757601</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.61822209400799</v>
+        <v>-4.729226349464131</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.058918505840658</v>
+        <v>0.8399038744275968</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1831082263804529</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.814423373421948</v>
+        <v>2.622085902698725</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.976854000079776</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.558331412365397</v>
+        <v>-4.669335667821538</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.15316501081987</v>
+        <v>0.9341503794068093</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.09367664225016153</v>
+        <v>-0.1232175447378595</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.92064801472968</v>
+        <v>2.728310544006456</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.99148173619582</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.656071956990371</v>
+        <v>-4.767076212446512</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.128696529085924</v>
+        <v>0.9096818976728633</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1095659203831417</v>
+        <v>-0.1391068228708396</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.925742183965935</v>
+        <v>2.733404713242712</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.990017717020491</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.8324097171133</v>
+        <v>-4.943413972569441</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.056697405861424</v>
+        <v>0.8376827744483633</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.315444582993769</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.818475508716849</v>
+        <v>2.626138037993626</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.98850933506042</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.755987670681374</v>
+        <v>-4.866991926137515</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.085757842474123</v>
+        <v>0.8667432110610624</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.315444582993769</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.816967126756778</v>
+        <v>2.624629656033555</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.988372202495856</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.711614539042805</v>
+        <v>-4.822618794498946</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.103369962564987</v>
+        <v>0.8843553311519261</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.2710714513552004</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.843453873175355</v>
+        <v>2.651116402452132</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.988372202495856</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.703660568748033</v>
+        <v>-4.814664824204174</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.106551550682896</v>
+        <v>0.887536919269835</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.2710714513552004</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.843453873175355</v>
+        <v>2.651116402452132</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.994753959523661</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.656004838186977</v>
+        <v>-4.767009093643118</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.131995599935123</v>
+        <v>0.912980968522062</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1938748183064469</v>
+        <v>-0.2234157207941448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.878429068539793</v>
+        <v>2.68609159781657</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.999646332898386</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.528320528392681</v>
+        <v>-4.639324783848822</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.187961697227566</v>
+        <v>0.9689470658145054</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06619050851215041</v>
+        <v>-0.09573141099984833</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.959932027791095</v>
+        <v>2.767594557067873</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.986401005374258</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.588987118795069</v>
+        <v>-4.69999137425121</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.150449733542483</v>
+        <v>0.9314351021294223</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1478888252306841</v>
+        <v>-0.177429727718382</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.897667710235848</v>
+        <v>2.705330239512624</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.990498707984886</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.544148717186671</v>
+        <v>-4.655152972642812</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.172482796796471</v>
+        <v>0.9534681653834101</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1433453922858146</v>
+        <v>-0.1728862947735125</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.904491472613398</v>
+        <v>2.712154001890175</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.994659647615964</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.644907352943669</v>
+        <v>-4.75591160839981</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.136340282124749</v>
+        <v>0.9173256507116889</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.23217096101282</v>
+        <v>-0.2617118635005179</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.855357071008273</v>
+        <v>2.663019600285049</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.000539250143802</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.600704515857768</v>
+        <v>-4.711708771313909</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.159901019486947</v>
+        <v>0.9408863880738862</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1879681239269196</v>
+        <v>-0.2175090264146175</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.88775837578765</v>
+        <v>2.695420905064427</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022906</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.998949250613049</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.637683543521211</v>
+        <v>-4.748687798977352</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.143519408890817</v>
+        <v>0.9245047774777566</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1509942221355891</v>
+        <v>-0.180535124623287</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.908352717331696</v>
+        <v>2.716015246608473</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.86392411404214</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.050197015796089</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.657741622386052</v>
+        <v>-4.768745877842193</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.186743942527921</v>
+        <v>0.9677293111148602</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1509942221355891</v>
+        <v>-0.180535124623287</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.959600482514736</v>
+        <v>2.767263011791512</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078283</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.048637720390342</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.617810949208161</v>
+        <v>-4.728815204664302</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.20115691639333</v>
+        <v>0.9821422849802695</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1110635489576987</v>
+        <v>-0.1406044514453966</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.981999591015723</v>
+        <v>2.7896621202925</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.8645188762324</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.043585948628612</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.566778856485634</v>
+        <v>-4.677783111941775</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.216517981720611</v>
+        <v>0.9975033503075506</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.06003145623517075</v>
+        <v>-0.08957235872286867</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.00756707488751</v>
+        <v>2.815229604164287</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
-        <v>3.060773352721317</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.501554675358428</v>
+        <v>-4.612558930814569</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.259795058264198</v>
+        <v>1.040780426851138</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.005192724892034872</v>
+        <v>-0.02434817759566305</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.063888987656538</v>
+        <v>2.871551516933315</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
-        <v>3.056734325020597</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.464127655287294</v>
+        <v>-4.575131910743435</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.270726838591932</v>
+        <v>1.051712207178872</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01044426292121653</v>
+        <v>-0.01909663956648139</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.063000882773327</v>
+        <v>2.870663412050104</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749924</v>
       </c>
       <c r="C1990" t="n">
-        <v>3.057991117351837</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.484239311322002</v>
+        <v>-4.595243566778143</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.263938968509289</v>
+        <v>1.044924337096229</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02147160791863573</v>
+        <v>-0.008069294569062191</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.070874082103019</v>
+        <v>2.878536611379796</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.218548888373048</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.430494496894798</v>
+        <v>-4.541498752350939</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.445994665301382</v>
+        <v>1.226980033888321</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03153491735909769</v>
+        <v>0.001994014871399774</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.237469838788507</v>
+        <v>3.045132368065284</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714888</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.338661797590865</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.406702928288656</v>
+        <v>-4.517707183744797</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.575624201961656</v>
+        <v>1.356609570548595</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.02578558347754206</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.37185768917001</v>
+        <v>3.179520218446787</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.330369773604724</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.380618844024847</v>
+        <v>-4.491623099480988</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.577765811681038</v>
+        <v>1.358751180267977</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.02578558347754206</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.363565665183869</v>
+        <v>3.171228194460646</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.328562969188504</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.3762845409678</v>
+        <v>-4.487288796423941</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.577692728487637</v>
+        <v>1.358678097074576</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.177435686796746</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.452748922759171</v>
+        <v>3.260411452035948</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.346117374915295</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.37981086046535</v>
+        <v>-4.478396335030657</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.593836606415408</v>
+        <v>1.379789487358681</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.177435686796746</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.470303328485962</v>
+        <v>3.277965857762739</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.337972422319879</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.548286977435227</v>
+        <v>-4.646872452000535</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.518301207032041</v>
+        <v>1.304254087975314</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1790287535678631</v>
+        <v>0.1494878510801652</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.445389674460597</v>
+        <v>3.253052203737374</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.408385083776723</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.850487448573644</v>
+        <v>-3.949072923138952</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.867833680033518</v>
+        <v>1.653786560976791</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.07913979170975449</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.473593500295195</v>
+        <v>3.281256029571971</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.399049106273627</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.827766344890491</v>
+        <v>-3.926351819455799</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.867586144003684</v>
+        <v>1.653539024946956</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.07913979170975449</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.464257522792099</v>
+        <v>3.271920052068876</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.557955232124796</v>
+        <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.968058944427684</v>
+        <v>-4.066644418992992</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.970375230039976</v>
+        <v>1.756328110983248</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.03161190533974023</v>
+        <v>-0.06115280782743815</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.538988088920953</v>
+        <v>3.34665061819773</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.595033054618443</v>
+        <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.122839951205939</v>
+        <v>-4.221425425771247</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.94554064982232</v>
+        <v>1.731493530765593</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.06497957939421634</v>
+        <v>-0.09452048188191425</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.556045306981913</v>
+        <v>3.363707836258691</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.591708410607988</v>
+        <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.190100395227856</v>
+        <v>-4.288685869793164</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.915311828203099</v>
+        <v>1.701264709146371</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1322400234161334</v>
+        <v>-0.1617809259038314</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.512364396558308</v>
+        <v>3.320026925835085</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766702530088372</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.60171456425273</v>
+        <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.085343975141726</v>
+        <v>-4.266214335754332</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.967220549882292</v>
+        <v>1.720259476406646</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1778638126396005</v>
+        <v>-0.02607544108786014</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.70843285183649</v>
+        <v>3.41145637036941</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.760438642162438</v>
+        <v>3.430189476409585</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.547379366678197</v>
+        <v>3.283916717885396</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.085343975141726</v>
+        <v>-4.266214335754332</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.967220549882292</v>
+        <v>1.720259476406646</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1778638126396005</v>
+        <v>-0.02607544108786014</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.540443163664565</v>
+        <v>3.276980514871763</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.0%</t>
+          <t>-701.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-52.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.7%</t>
+          <t>455.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.2%</t>
+          <t>-571.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-281.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.4%</t>
+          <t>-510.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-204.2%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>158.5%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.8%</t>
+          <t>-186.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.6%</t>
+          <t>-211.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-118.3%</t>
+          <t>-110.4%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8280060818753194</v>
+        <v>-0.926522492321503</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.789769905262851</v>
+        <v>2.750363341084377</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.035571866266931</v>
+        <v>-1.134088276713115</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.704568387625446</v>
+        <v>2.665161823446973</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.453325889813768</v>
+        <v>-1.551842300259952</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.535393669711775</v>
+        <v>2.495987105533301</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.7434575564192</v>
+        <v>-1.841973966865383</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.419207219668524</v>
+        <v>2.379800655490051</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.951461614772277</v>
+        <v>-2.049978025218461</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.340897740881218</v>
+        <v>2.301491176702745</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.162874035660252</v>
+        <v>-2.261390446106435</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251414228864017</v>
+        <v>2.212007664685543</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.528942762804905</v>
+        <v>-2.627459173251088</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098071037312605</v>
+        <v>2.058664473134131</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.737433544256589</v>
+        <v>-2.835949954702773</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035013014470699</v>
+        <v>1.995606450292225</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.984634729021811</v>
+        <v>-3.083151139467994</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944231290973179</v>
+        <v>1.904824726794705</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.477019757045908</v>
+        <v>-3.575536167492091</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748383671807272</v>
+        <v>1.708977107628799</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.86220014797598</v>
+        <v>-3.960716558422163</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592854054248107</v>
+        <v>1.553447490069633</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.112070827990562</v>
+        <v>-4.210587238436744</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49467490569689</v>
+        <v>1.455268341518417</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.318582604877583</v>
+        <v>-4.417099015323766</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.40817625359834</v>
+        <v>1.368769689419866</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.637926679958085</v>
+        <v>-4.736443090404268</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282211550266398</v>
+        <v>1.242804986087925</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.069732473107872</v>
+        <v>-5.168248883554055</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.056415556295414</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.304426467240424</v>
+        <v>-5.402942877686607</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>0.9508227336444839</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.640089114470877</v>
+        <v>-5.73860552491706</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>0.815138266408268</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.00371535937119</v>
+        <v>-6.102231769817373</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.6761753286823842</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.46735915245612</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.5293788906327168</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.875947929636799</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.3647049237752045</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-7.152524029952631</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.2492599161203319</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.568915904239629</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.08069721701441068</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.813187304966698</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>-0.006752652607738163</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-8.018438324203458</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>-0.09275349515674769</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-8.182018202387843</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>-0.1597805263755006</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.478679544198041</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.2746660871703717</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.665399252507344</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.3533802750284956</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-9.048400641249975</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.5066829318471324</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-9.23027043223501</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.576859332269716</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.589800754739011</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.7153211579732663</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.640149818193233</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.7275447633977778</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.737769095614629</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.7635507237445673</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.885295183620272</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.8196676026252523</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-10.08955335895014</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.8958576756385552</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-10.1638863352103</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.9211083116581853</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-10.09041650354285</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.8763486774977842</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-10.26554092092939</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.9318432237048846</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.49999301494388</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-1.032843226212277</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.60436774597033</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-1.081265309396831</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.65715390157066</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-1.101263981798406</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.78319069493895</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.148984970516607</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.73117518097013</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.124188429242681</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.87284702269425</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.18233239283107</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.82325617826942</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.147442644896265</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.81044878526465</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.155370821341038</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.58460363254523</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-1.055453687217065</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.46002497620764</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-1.004483080125969</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.51292026425193</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-1.023007421181576</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.44078708896405</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.9884204468277868</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.3694206963544</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.9696111521777935</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-10.27596166236918</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.9421110198966107</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-10.00871986150078</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.8370488600486259</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.910812822824287</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.7981863595514902</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.886859281848329</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.7879364370156137</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.622799343525532</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.695572777848247</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.915719720020695</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.415527962106613</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.875535421654504</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.3991106188722955</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.712135550715141</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.3343838492757931</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.478654328485542</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.2330669315461007</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.328987937478027</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.1760925854560544</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-8.19671246384714</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.1278149092566725</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-8.040974131287399</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>-0.06270451554513912</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.791974332603818</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.04980174515195168</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.897564322376923</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>-0.1204101803565085</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.916299224495519</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>-0.07935979932686088</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.76835918308792</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.1400627054519887</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.715389660833932</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.1275888828038716</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.671841254063241</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>-0.1171301321906886</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.429692860609383</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>-0.005808420428002226</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.321433723486861</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.03202735488020148</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-7.198142588669731</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.07884190281763059</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-7.176993389766287</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.09500256061633294</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.933227947782843</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.1882894457567614</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.831465127505548</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.2311188877876953</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.581614733556473</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.3238011203510274</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.40572264108904</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.3977570808586495</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-6.234276178066577</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.4796631721221885</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-6.159986612328238</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.5083994760338211</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-6.096350870094303</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.538548573981712</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.984924110768383</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.564313536495876</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.744493613963523</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.6622288118426973</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.672251045792328</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.6950551529459954</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.61925272351094</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.7169330657758906</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.510447838031213</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.757453091187775</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.290427039994203</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.8470404474131934</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-5.157559350930925</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>0.9160817058403277</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-5.037386267566426</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>0.965296783626429</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.892714122466689</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.033253744227764</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.952588949824381</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>0.9953413046861128</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.825431782556716</v>
+        <v>-4.865789452045373</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.068604664915746</v>
+        <v>1.052461597120282</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.827901489018522</v>
+        <v>-4.868259158507179</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.067689183704435</v>
+        <v>1.051546115908972</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.896271675342533</v>
+        <v>-4.936629344831189</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.051348031649533</v>
+        <v>1.03520496385407</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.004809856258666</v>
+        <v>-5.045167525747323</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9983694679149711</v>
+        <v>0.9822264001195076</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.035803015587372</v>
+        <v>-5.076160685076029</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8106817692238755</v>
+        <v>0.7945387014284124</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.860328755794903</v>
+        <v>-4.90068642528356</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8854387051326509</v>
+        <v>0.8692956373371876</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.971265008436152</v>
+        <v>-5.011622677924809</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8168062328373584</v>
+        <v>0.8006631650418949</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.93760146296387</v>
+        <v>-4.977959132452527</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8334030362461768</v>
+        <v>0.8172599684507134</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.877748843760147</v>
+        <v>-4.918106513248803</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8675164703597984</v>
+        <v>0.8513734025643351</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.791505380733769</v>
+        <v>-4.831863050222426</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8969601261442099</v>
+        <v>0.8808170583487465</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.836812200132749</v>
+        <v>-4.877169869621405</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8706131738291436</v>
+        <v>0.8544701060336801</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.86584530483505</v>
+        <v>-4.906202974323707</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8595518049813247</v>
+        <v>0.8434087371858612</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.77303482338419</v>
+        <v>-4.813392492872847</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8259486894530341</v>
+        <v>0.8098056216575706</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.817424292713618</v>
+        <v>-4.857781962202274</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8100663776458639</v>
+        <v>0.7939233098504006</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.796591975741188</v>
+        <v>-4.745110743966024</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8134750129465589</v>
+        <v>0.8340675056566236</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2983260026259584</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.553472625981207</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.684214974558515</v>
+        <v>-4.632733742783351</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8639171092502953</v>
+        <v>0.88450960196036</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2983260026259584</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.558963921811874</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.711995372459867</v>
+        <v>-4.660514140684704</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8643021518582934</v>
+        <v>0.8848946445683581</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3261064005273114</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.553792884839601</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.794996653485146</v>
+        <v>-4.743515421709983</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6694573594488351</v>
+        <v>0.6900498521588998</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3446772850544852</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.38100607412395</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.903610731928477</v>
+        <v>-4.852129500153314</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7461613887907084</v>
+        <v>0.7667538815007728</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3446772850544852</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.501155734843155</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.99020931490958</v>
+        <v>-4.938728083134417</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.72603498170059</v>
+        <v>0.7466274744106547</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3446772850544852</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.515668760945478</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.951825652351429</v>
+        <v>-4.900344420576266</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7388078880662192</v>
+        <v>0.7594003807762839</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.306293622496334</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.536118399822738</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.774709322316263</v>
+        <v>-4.7232280905411</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8063834489255877</v>
+        <v>0.8269759416356521</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.306293622496334</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.53284742866804</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.819801567149809</v>
+        <v>-4.768320335374646</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7890299427540823</v>
+        <v>0.809622435464147</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3681896656657238</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.496393194528319</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.640426145911041</v>
+        <v>-4.588944914135878</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8545670865560038</v>
+        <v>0.8751595792660685</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2114129074950051</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.584246224737165</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.685440359431647</v>
+        <v>-4.633959127656484</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8173688564793513</v>
+        <v>0.837961349189416</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2417618028096097</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.546844342879992</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.952444869704082</v>
+        <v>-4.900963637928919</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7162586147093231</v>
+        <v>0.7368511074193878</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4361248408525583</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.435918082393168</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.053642651141255</v>
+        <v>-5.002161419366091</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6749834240309553</v>
+        <v>0.69557591674102</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5045336543978776</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.394076716162478</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.021167064970482</v>
+        <v>-4.969685833195319</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6855736200535811</v>
+        <v>0.7061661127636456</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5045336543978776</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.391676677716795</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.002128937263185</v>
+        <v>-4.950647705488022</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6897135903447449</v>
+        <v>0.7103060830548094</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5627172657290722</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.353291230126323</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.994262181648599</v>
+        <v>-4.98177433663864</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8704421615292597</v>
+        <v>0.8754372995332427</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5627172657290722</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.530873099065003</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.008128942982517</v>
+        <v>-4.995641097972558</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8657287859818261</v>
+        <v>0.8707239239858091</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6005751824628951</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.508991678010843</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.028386241511475</v>
+        <v>-5.015898396501516</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8636343969671687</v>
+        <v>0.8686295349711517</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6005751824628951</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.515000208407769</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.880643271276472</v>
+        <v>-4.868155426266513</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.001884232853192</v>
+        <v>1.006879370857175</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4327678252280119</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.694837270540721</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.982657953807694</v>
+        <v>-4.970170108797735</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9638719813721843</v>
+        <v>0.9688671193761671</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4327678252280119</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.697630892072202</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.976505247754909</v>
+        <v>-4.96401740274495</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9669954121849564</v>
+        <v>0.9719905501889392</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4266151191752277</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.701984864095531</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.993314545905411</v>
+        <v>-4.980826700895452</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9593521696648659</v>
+        <v>0.9643473076688487</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4434244173257293</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.69097976194534</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.931016547129289</v>
+        <v>-4.91852870211933</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.050606922972136</v>
+        <v>1.055602060976119</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3811264185496073</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.794694115007835</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.729226349464131</v>
+        <v>-4.716738504454172</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8399038744275968</v>
+        <v>0.8448990124315798</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1831082263804529</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.622085902698725</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.669335667821538</v>
+        <v>-4.656847822811579</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9341503794068093</v>
+        <v>0.9391455174107923</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1232175447378595</v>
+        <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.728310544006456</v>
+        <v>2.746035085499075</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.767076212446512</v>
+        <v>-4.754588367436553</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9096818976728633</v>
+        <v>0.9146770356768461</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1391068228708396</v>
+        <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.733404713242712</v>
+        <v>2.751129254735331</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.943413972569441</v>
+        <v>-4.930926127559482</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8376827744483633</v>
+        <v>0.8426779124523462</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.315444582993769</v>
+        <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.626138037993626</v>
+        <v>2.643862579486245</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.866991926137515</v>
+        <v>-4.854504081127556</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8667432110610624</v>
+        <v>0.8717383490650454</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.315444582993769</v>
+        <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.624629656033555</v>
+        <v>2.642354197526173</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.822618794498946</v>
+        <v>-4.810130949488987</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8843553311519261</v>
+        <v>0.8893504691559091</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2710714513552004</v>
+        <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.651116402452132</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.814664824204174</v>
+        <v>-4.802176979194215</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.887536919269835</v>
+        <v>0.892532057273818</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2710714513552004</v>
+        <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.651116402452132</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.767009093643118</v>
+        <v>-4.754521248633159</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.912980968522062</v>
+        <v>0.917976106526045</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2234157207941448</v>
+        <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.68609159781657</v>
+        <v>2.703816139309189</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.639324783848822</v>
+        <v>-4.626836938838863</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9689470658145054</v>
+        <v>0.9739422038184884</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.09573141099984833</v>
+        <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.767594557067873</v>
+        <v>2.785319098560491</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.69999137425121</v>
+        <v>-4.687503529241251</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9314351021294223</v>
+        <v>0.936430240133405</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.177429727718382</v>
+        <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.705330239512624</v>
+        <v>2.723054781005243</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.655152972642812</v>
+        <v>-4.642665127632853</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9534681653834101</v>
+        <v>0.9584633033873931</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1728862947735125</v>
+        <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.712154001890175</v>
+        <v>2.729878543382794</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.75591160839981</v>
+        <v>-4.585404172191267</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9173256507116889</v>
+        <v>0.9855286251951054</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2617118635005179</v>
+        <v>-0.1135202505092958</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.663019600285049</v>
+        <v>2.751934568079783</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.711708771313909</v>
+        <v>-4.541201335105367</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9408863880738862</v>
+        <v>1.009089362557303</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2175090264146175</v>
+        <v>-0.06931741342339531</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.695420905064427</v>
+        <v>2.784335872859161</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.748687798977352</v>
+        <v>-4.57818036276881</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9245047774777566</v>
+        <v>0.9927077519611727</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.180535124623287</v>
+        <v>-0.03234351163206478</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.716015246608473</v>
+        <v>2.804930214403206</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.768745877842193</v>
+        <v>-4.598238441633651</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9677293111148602</v>
+        <v>1.035932285598276</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.180535124623287</v>
+        <v>-0.03234351163206478</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.767263011791512</v>
+        <v>2.856177979586246</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.728815204664302</v>
+        <v>-4.55830776845576</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9821422849802695</v>
+        <v>1.050345259463686</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1406044514453966</v>
+        <v>0.00758716154582556</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.7896621202925</v>
+        <v>2.878577088087233</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.677783111941775</v>
+        <v>-4.507275675733233</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9975033503075506</v>
+        <v>1.065706324790967</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.08957235872286867</v>
+        <v>0.05861925426835352</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.815229604164287</v>
+        <v>2.90414457195902</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.612558930814569</v>
+        <v>-4.442051494606027</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.040780426851138</v>
+        <v>1.108983401334554</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.02434817759566305</v>
+        <v>0.1238434353955591</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.871551516933315</v>
+        <v>2.960466484728048</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.575131910743435</v>
+        <v>-4.404624474534893</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.051712207178872</v>
+        <v>1.119915181662288</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.01909663956648139</v>
+        <v>0.1290949734247408</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.870663412050104</v>
+        <v>2.959578379844838</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.595243566778143</v>
+        <v>-4.424736130569602</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.044924337096229</v>
+        <v>1.113127311579645</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.008069294569062191</v>
+        <v>0.14012231842216</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.878536611379796</v>
+        <v>2.967451579174529</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.541498752350939</v>
+        <v>-4.370991316142397</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.226980033888321</v>
+        <v>1.295183008371737</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.001994014871399774</v>
+        <v>0.150185627862622</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.045132368065284</v>
+        <v>3.134047335860017</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.517707183744797</v>
+        <v>-4.347199747536255</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.356609570548595</v>
+        <v>1.424812545032011</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.02578558347754206</v>
+        <v>0.1739771964687643</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.179520218446787</v>
+        <v>3.26843518624152</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.491623099480988</v>
+        <v>-4.321115663272447</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.358751180267977</v>
+        <v>1.426954154751394</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.02578558347754206</v>
+        <v>0.1739771964687643</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.171228194460646</v>
+        <v>3.260143162255379</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.487288796423941</v>
+        <v>-4.316781360215399</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.358678097074576</v>
+        <v>1.426881071557992</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.177435686796746</v>
+        <v>0.3256272997879682</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.260411452035948</v>
+        <v>3.349326419830681</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.478396335030657</v>
+        <v>-4.307888898822116</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.379789487358681</v>
+        <v>1.447992461842097</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.177435686796746</v>
+        <v>0.3256272997879682</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.277965857762739</v>
+        <v>3.366880825557472</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.646872452000535</v>
+        <v>-4.476365015791993</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.304254087975314</v>
+        <v>1.37245706245873</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1494878510801652</v>
+        <v>0.2976794640713874</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.253052203737374</v>
+        <v>3.341967171532108</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.949072923138952</v>
+        <v>-3.77856548693041</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.653786560976791</v>
+        <v>1.721989535460207</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.07913979170975449</v>
+        <v>0.2273314047009767</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.281256029571971</v>
+        <v>3.370170997366705</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.926351819455799</v>
+        <v>-3.755844383247257</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.653539024946956</v>
+        <v>1.721741999430372</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.07913979170975449</v>
+        <v>0.2273314047009767</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.271920052068876</v>
+        <v>3.360835019863609</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.066644418992992</v>
+        <v>-3.89613698278445</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.756328110983248</v>
+        <v>1.824531085466664</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.06115280782743815</v>
+        <v>0.08703880516378404</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.34665061819773</v>
+        <v>3.435565585992463</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.221425425771247</v>
+        <v>-4.050917989562705</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.731493530765593</v>
+        <v>1.799696505249009</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.09452048188191425</v>
+        <v>0.05367113110930793</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.363707836258691</v>
+        <v>3.452622804053424</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.288685869793164</v>
+        <v>-4.118178433584622</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.701264709146371</v>
+        <v>1.769467683629787</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1617809259038314</v>
+        <v>-0.01358931291260917</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.320026925835085</v>
+        <v>3.408941893629819</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088372</v>
+        <v>3.846424076018487</v>
       </c>
       <c r="C2002" t="n">
         <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.266214335754332</v>
+        <v>-4.09570689954579</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.720259476406646</v>
+        <v>1.788462450890062</v>
       </c>
       <c r="F2002" t="n">
-        <v>-0.02607544108786014</v>
+        <v>0.122116171903362</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.41145637036941</v>
+        <v>3.500371338164143</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.430189476409585</v>
+        <v>3.591045602522235</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.283916717885396</v>
+        <v>3.363113649180194</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.266214335754332</v>
+        <v>-4.09570689954579</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.720259476406646</v>
+        <v>1.788462450890062</v>
       </c>
       <c r="F2003" t="n">
-        <v>-0.02607544108786014</v>
+        <v>0.122116171903362</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.276980514871763</v>
+        <v>3.356177446166562</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-701.9%</t>
+          <t>-692.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.9%</t>
+          <t>459.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-571.1%</t>
+          <t>-585.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.1%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.8%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-510.0%</t>
+          <t>119.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-203.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-186.3%</t>
+          <t>-172.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.8%</t>
+          <t>-222.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-110.4%</t>
+          <t>-104.1%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.926522492321503</v>
+        <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.750363341084377</v>
+        <v>2.789769905262851</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.134088276713115</v>
+        <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.665161823446973</v>
+        <v>2.704568387625446</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.551842300259952</v>
+        <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.495987105533301</v>
+        <v>2.535393669711775</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.841973966865383</v>
+        <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.379800655490051</v>
+        <v>2.419207219668524</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-2.049978025218461</v>
+        <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.301491176702745</v>
+        <v>2.340897740881218</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.261390446106435</v>
+        <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.212007664685543</v>
+        <v>2.251414228864017</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.627459173251088</v>
+        <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.058664473134131</v>
+        <v>2.098071037312605</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.835949954702773</v>
+        <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>1.995606450292225</v>
+        <v>2.035013014470699</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.083151139467994</v>
+        <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.904824726794705</v>
+        <v>1.944231290973179</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.575536167492091</v>
+        <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.708977107628799</v>
+        <v>1.748383671807272</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.960716558422163</v>
+        <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.553447490069633</v>
+        <v>1.592854054248107</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.210587238436744</v>
+        <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.455268341518417</v>
+        <v>1.49467490569689</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.417099015323766</v>
+        <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.368769689419866</v>
+        <v>1.40817625359834</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.736443090404268</v>
+        <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.242804986087925</v>
+        <v>1.282211550266398</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.168248883554055</v>
+        <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.056415556295414</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.402942877686607</v>
+        <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9508227336444839</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.73860552491706</v>
+        <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.815138266408268</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.102231769817373</v>
+        <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6761753286823842</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.46735915245612</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5293788906327168</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.875947929636799</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3647049237752045</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.152524029952631</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2492599161203319</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.568915904239629</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.08069721701441068</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.813187304966698</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.006752652607738163</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.018438324203458</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09275349515674769</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.182018202387843</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1597805263755006</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.478679544198041</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2746660871703717</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.665399252507344</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3533802750284956</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.048400641249975</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5066829318471324</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.23027043223501</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.576859332269716</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.589800754739011</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7153211579732663</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.640149818193233</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7275447633977778</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.737769095614629</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7635507237445673</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.885295183620272</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8196676026252523</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.08955335895014</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8958576756385552</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.1638863352103</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9211083116581853</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.09041650354285</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8763486774977842</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.26554092092939</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9318432237048846</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.49999301494388</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.032843226212277</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.60436774597033</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.081265309396831</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.65715390157066</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.101263981798406</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.78319069493895</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.148984970516607</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.73117518097013</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.124188429242681</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.87284702269425</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.18233239283107</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.82325617826942</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.147442644896265</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.81044878526465</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.155370821341038</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.58460363254523</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.055453687217065</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.46002497620764</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.004483080125969</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.51292026425193</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.023007421181576</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.44078708896405</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9884204468277868</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.3694206963544</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9696111521777935</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.27596166236918</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9421110198966107</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.00871986150078</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8370488600486259</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.910812822824287</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7981863595514902</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.886859281848329</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7879364370156137</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.622799343525532</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.695572777848247</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.915719720020695</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.415527962106613</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.875535421654504</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3991106188722955</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.712135550715141</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3343838492757931</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.478654328485542</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2330669315461007</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.328987937478027</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1760925854560544</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.19671246384714</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1278149092566725</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.040974131287399</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.06270451554513912</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.791974332603818</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.04980174515195168</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.897564322376923</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1204101803565085</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.916299224495519</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07935979932686088</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76835918308792</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1400627054519887</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.715389660833932</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1275888828038716</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.671841254063241</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1171301321906886</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.429692860609383</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.005808420428002226</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.321433723486861</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03202735488020148</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.198142588669731</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.07884190281763059</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.176993389766287</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.09500256061633294</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.933227947782843</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1882894457567614</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.831465127505548</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2311188877876953</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.581614733556473</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3238011203510274</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.40572264108904</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3977570808586495</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.234276178066577</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4796631721221885</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.159986612328238</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5083994760338211</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.096350870094303</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.538548573981712</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.984924110768383</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.564313536495876</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.744493613963523</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6622288118426973</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.672251045792328</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6950551529459954</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.61925272351094</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7169330657758906</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.510447838031213</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.757453091187775</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.290427039994203</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8470404474131934</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.157559350930925</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9160817058403277</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.037386267566426</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.965296783626429</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.892714122466689</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.033253744227764</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.952588949824381</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9953413046861128</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.865789452045373</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.052461597120282</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.868259158507179</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.051546115908972</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.936629344831189</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.03520496385407</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.045167525747323</v>
+        <v>-4.946651115301141</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9822264001195076</v>
+        <v>1.021632964297981</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.076160685076029</v>
+        <v>-4.977644274629847</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7945387014284124</v>
+        <v>0.8339452656068858</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.90068642528356</v>
+        <v>-4.802170014837378</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8692956373371876</v>
+        <v>0.9087022015156609</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.011622677924809</v>
+        <v>-4.913106267478627</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8006631650418949</v>
+        <v>0.8400697292203685</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.977959132452527</v>
+        <v>-4.879442722006345</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8172599684507134</v>
+        <v>0.8566665326291869</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.918106513248803</v>
+        <v>-4.819590102802621</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8513734025643351</v>
+        <v>0.8907799667428087</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.831863050222426</v>
+        <v>-4.733346639776244</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8808170583487465</v>
+        <v>0.92022362252722</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.877169869621405</v>
+        <v>-4.778653459175223</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8544701060336801</v>
+        <v>0.8938766702121537</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.906202974323707</v>
+        <v>-4.807686563877525</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8434087371858612</v>
+        <v>0.8828153013643347</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.813392492872847</v>
+        <v>-4.714876082426665</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8098056216575706</v>
+        <v>0.8492121858360442</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.857781962202274</v>
+        <v>-4.759265551756092</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7939233098504006</v>
+        <v>0.8333298740288742</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.745110743966024</v>
+        <v>-4.646594333519842</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8340675056566236</v>
+        <v>0.8734740698350971</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.632733742783351</v>
+        <v>-4.623842989996371</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.88450960196036</v>
+        <v>0.888065903075153</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.660514140684704</v>
+        <v>-4.651623387897724</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8848946445683581</v>
+        <v>0.8884509456831509</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.743515421709983</v>
+        <v>-4.734624668923002</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6900498521588998</v>
+        <v>0.6936061532736926</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.852129500153314</v>
+        <v>-4.843238747366334</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7667538815007728</v>
+        <v>0.7703101826155658</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.938728083134417</v>
+        <v>-4.929837330347437</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7466274744106547</v>
+        <v>0.7501837755254477</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.900344420576266</v>
+        <v>-4.891453667789285</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7594003807762839</v>
+        <v>0.7629566818910767</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.7232280905411</v>
+        <v>-4.714337337754119</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8269759416356521</v>
+        <v>0.8305322427504451</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.768320335374646</v>
+        <v>-4.759429582587665</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.809622435464147</v>
+        <v>0.8131787365789398</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.588944914135878</v>
+        <v>-4.580054161348897</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8751595792660685</v>
+        <v>0.8787158803808612</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.633959127656484</v>
+        <v>-4.625068374869503</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.837961349189416</v>
+        <v>0.8415176503042088</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.900963637928919</v>
+        <v>-4.892072885141938</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7368511074193878</v>
+        <v>0.7404074085341805</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.002161419366091</v>
+        <v>-4.993270666579111</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.69557591674102</v>
+        <v>0.6991322178558128</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.969685833195319</v>
+        <v>-4.960795080408339</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7061661127636456</v>
+        <v>0.7097224138784384</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.950647705488022</v>
+        <v>-4.941756952701041</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7103060830548094</v>
+        <v>0.7138623841696023</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.98177433663864</v>
+        <v>-4.97288358385166</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8754372995332427</v>
+        <v>0.8789936006480354</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.995641097972558</v>
+        <v>-4.98397560179564</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8707239239858091</v>
+        <v>0.875390122456577</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4946961267436525</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.572519111442389</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.015898396501516</v>
+        <v>-5.004232900324598</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8686295349711517</v>
+        <v>0.8732957334419198</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4946961267436525</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.578527641839315</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.868155426266513</v>
+        <v>-4.856489930089595</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.006879370857175</v>
+        <v>1.011545569327943</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3268887695087693</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.758364703972267</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.970170108797735</v>
+        <v>-4.958504612620817</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9688671193761671</v>
+        <v>0.9735333178469352</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3268887695087693</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.761158325503748</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394736</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.96401740274495</v>
+        <v>-4.952351906568032</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9719905501889392</v>
+        <v>0.9766567486597073</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.320736063455985</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.765512297527077</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.980826700895452</v>
+        <v>-4.969161204718534</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9643473076688487</v>
+        <v>0.9690135061396168</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3375453616064867</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.754507195376886</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.91852870211933</v>
+        <v>-4.906863205942412</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.055602060976119</v>
+        <v>1.060268259446886</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3375453616064867</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.820842749173707</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992197</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.716738504454172</v>
+        <v>-4.705073008277254</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8448990124315798</v>
+        <v>0.8495652109023477</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1395271694373323</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.648234536864598</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.656847822811579</v>
+        <v>-4.645182326634661</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9391455174107923</v>
+        <v>0.9438117158815602</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.09367664225016153</v>
+        <v>-0.07963648779473881</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746035085499075</v>
+        <v>2.754459178172329</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319551</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.754588367436553</v>
+        <v>-4.742922871259635</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9146770356768461</v>
+        <v>0.9193432341476142</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1095659203831417</v>
+        <v>-0.095525765927719</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751129254735331</v>
+        <v>2.759553347408584</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.930926127559482</v>
+        <v>-4.919260631382564</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8426779124523462</v>
+        <v>0.8473441109231141</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.2718635260506484</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.643862579486245</v>
+        <v>2.652286672159498</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.854504081127556</v>
+        <v>-4.842838584950638</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8717383490650454</v>
+        <v>0.8764045475358133</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.2718635260506484</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642354197526173</v>
+        <v>2.650778290199427</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.810130949488987</v>
+        <v>-4.798465453312069</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8893504691559091</v>
+        <v>0.894016667626677</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.2274903944120798</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668840943944751</v>
+        <v>2.677265036618004</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.802176979194215</v>
+        <v>-4.790511483017297</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.892532057273818</v>
+        <v>0.8971982557445859</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.2274903944120798</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668840943944751</v>
+        <v>2.677265036618004</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.754521248633159</v>
+        <v>-4.742855752456241</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.917976106526045</v>
+        <v>0.9226423049968129</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1938748183064469</v>
+        <v>-0.1798346638510241</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.703816139309189</v>
+        <v>2.712240231982442</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.626836938838863</v>
+        <v>-4.615171442661945</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9739422038184884</v>
+        <v>0.9786084022892563</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06619050851215041</v>
+        <v>-0.05215035405672769</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785319098560491</v>
+        <v>2.793743191233745</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314554</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.687503529241251</v>
+        <v>-4.675838033064334</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.936430240133405</v>
+        <v>0.9410964386041727</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1478888252306841</v>
+        <v>-0.1338486707752614</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.723054781005243</v>
+        <v>2.731478873678497</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.642665127632853</v>
+        <v>-4.630999631455936</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9584633033873931</v>
+        <v>0.9631295018581607</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1433453922858146</v>
+        <v>-0.1293052378303919</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.729878543382794</v>
+        <v>2.738302636056047</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.585404172191267</v>
+        <v>-4.731758267212934</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9855286251951054</v>
+        <v>0.9269869871864393</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1135202505092958</v>
+        <v>-0.2181308065573973</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.751934568079783</v>
+        <v>2.689168234450922</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.541201335105367</v>
+        <v>-4.687555430127033</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.009089362557303</v>
+        <v>0.9505477245486367</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06931741342339531</v>
+        <v>-0.1739279694714969</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.784335872859161</v>
+        <v>2.721569539230299</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022906</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.57818036276881</v>
+        <v>-4.724534457790476</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9927077519611727</v>
+        <v>0.9341661139525073</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.03234351163206478</v>
+        <v>-0.1369540676801663</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.804930214403206</v>
+        <v>2.742163880774345</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86392411404214</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.598238441633651</v>
+        <v>-4.744592536655317</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.035932285598276</v>
+        <v>0.9773906475896106</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.03234351163206478</v>
+        <v>-0.1369540676801663</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.856177979586246</v>
+        <v>2.793411645957385</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078283</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.55830776845576</v>
+        <v>-4.704661863477426</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.050345259463686</v>
+        <v>0.9918036214550199</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.00758716154582556</v>
+        <v>-0.09702339450227598</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.878577088087233</v>
+        <v>2.815810754458372</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.8645188762324</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.507275675733233</v>
+        <v>-4.653629770754899</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.065706324790967</v>
+        <v>1.007164686782301</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.05861925426835352</v>
+        <v>-0.04599130177974803</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.90414457195902</v>
+        <v>2.841378238330159</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.442051494606027</v>
+        <v>-4.588405589627693</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.108983401334554</v>
+        <v>1.050441763325888</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1238434353955591</v>
+        <v>0.0192328793474576</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.960466484728048</v>
+        <v>2.897700151099187</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.404624474534893</v>
+        <v>-4.550978569556559</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.119915181662288</v>
+        <v>1.061373543653622</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1290949734247408</v>
+        <v>0.02448441737663926</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.959578379844838</v>
+        <v>2.896812046215977</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749924</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.424736130569602</v>
+        <v>-4.571090225591267</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.113127311579645</v>
+        <v>1.054585673570979</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.14012231842216</v>
+        <v>0.03551176237405845</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.967451579174529</v>
+        <v>2.904685245545668</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.370991316142397</v>
+        <v>-4.517345411164063</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.295183008371737</v>
+        <v>1.236641370363072</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.150185627862622</v>
+        <v>0.04557507181452042</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.134047335860017</v>
+        <v>3.071281002231157</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714888</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.347199747536255</v>
+        <v>-4.493553842557921</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.424812545032011</v>
+        <v>1.366270907023346</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1739771964687643</v>
+        <v>0.06936664042066271</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.26843518624152</v>
+        <v>3.205668852612659</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.321115663272447</v>
+        <v>-4.467469758294112</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.426954154751394</v>
+        <v>1.368412516742728</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1739771964687643</v>
+        <v>0.06936664042066271</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.260143162255379</v>
+        <v>3.197376828626518</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.316781360215399</v>
+        <v>-4.463135455237064</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.426881071557992</v>
+        <v>1.368339433549327</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3256272997879682</v>
+        <v>0.2210167437398666</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.349326419830681</v>
+        <v>3.28656008620182</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.307888898822116</v>
+        <v>-4.454242993843781</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.447992461842097</v>
+        <v>1.389450823833431</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3256272997879682</v>
+        <v>0.2210167437398666</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.366880825557472</v>
+        <v>3.304114491928611</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702629</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.476365015791993</v>
+        <v>-4.622719110813659</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.37245706245873</v>
+        <v>1.313915424450064</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2976794640713874</v>
+        <v>0.1930689080232859</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.341967171532108</v>
+        <v>3.279200837903247</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.77856548693041</v>
+        <v>-3.924919581952075</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.721989535460207</v>
+        <v>1.663447897451541</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2273314047009767</v>
+        <v>0.1227208486528751</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.370170997366705</v>
+        <v>3.307404663737844</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.755844383247257</v>
+        <v>-3.902198478268923</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.721741999430372</v>
+        <v>1.663200361421707</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2273314047009767</v>
+        <v>0.1227208486528751</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.360835019863609</v>
+        <v>3.298068686234748</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.89613698278445</v>
+        <v>-4.042491077806115</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.824531085466664</v>
+        <v>1.765989447457999</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.08703880516378404</v>
+        <v>-0.01757175088431751</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.435565585992463</v>
+        <v>3.372799252363602</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.050917989562705</v>
+        <v>-4.197272084584371</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.799696505249009</v>
+        <v>1.741154867240343</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.05367113110930793</v>
+        <v>-0.05093942493879361</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452622804053424</v>
+        <v>3.389856470424563</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557225</v>
       </c>
       <c r="C2001" t="n">
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.118178433584622</v>
+        <v>-4.264532528606288</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.769467683629787</v>
+        <v>1.710926045621122</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.01358931291260917</v>
+        <v>-0.1181998689607107</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.408941893629819</v>
+        <v>3.346175560000958</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.846424076018487</v>
+        <v>3.766702530088376</v>
       </c>
       <c r="C2002" t="n">
         <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.09570689954579</v>
+        <v>-4.242060994567455</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.788462450890062</v>
+        <v>1.729920812881396</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.122116171903362</v>
+        <v>0.0175056158552605</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.500371338164143</v>
+        <v>3.437605004535282</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.591045602522235</v>
+        <v>3.793386779707436</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.363113649180194</v>
+        <v>3.426126353051396</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.09570689954579</v>
+        <v>-4.242060994567455</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.788462450890062</v>
+        <v>1.729920812881396</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.122116171903362</v>
+        <v>0.0175056158552605</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.356177446166562</v>
+        <v>3.419190150037763</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.0%</t>
+          <t>-691.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.7%</t>
+          <t>459.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.8%</t>
+          <t>-558.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>119.9%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-203.2%</t>
+          <t>-192.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.5%</t>
+          <t>-300.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.6%</t>
+          <t>-171.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.2%</t>
+          <t>-219.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-104.1%</t>
+          <t>-100.4%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.162874035660252</v>
+        <v>-2.161955619248791</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251414228864017</v>
+        <v>2.251781595428601</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.5817759354884754</v>
+        <v>0.5826943518999366</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.46598582873495</v>
+        <v>3.466536878581827</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.528942762804905</v>
+        <v>-2.528024346393444</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098071037312605</v>
+        <v>2.098438403877189</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2157072083438227</v>
+        <v>0.2166256247552839</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239428891754608</v>
+        <v>3.239979941601484</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.737433544256589</v>
+        <v>-2.736515127845128</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035013014470699</v>
+        <v>2.035380381035283</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.007216426892138306</v>
+        <v>0.008134843303599482</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.134672712622365</v>
+        <v>3.135223762469242</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.984634729021811</v>
+        <v>-2.98371631261035</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944231290973179</v>
+        <v>1.944598657537763</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.02736978039095073</v>
+        <v>0.0282881968024119</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.154863475130221</v>
+        <v>3.155414524977098</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.477019757045908</v>
+        <v>-3.476101340634447</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748383671807272</v>
+        <v>1.748751038371857</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.4640968312216848</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.860538850359495</v>
+        <v>2.861089900206372</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.86220014797598</v>
+        <v>-3.861281731564519</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592854054248107</v>
+        <v>1.593221420812691</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.4640968312216848</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859081389172359</v>
+        <v>2.859632439019235</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.112070827990562</v>
+        <v>-4.1111524115791</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49467490569689</v>
+        <v>1.495042272261474</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4287525278026827</v>
+        <v>-0.4278341113912216</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882608144525252</v>
+        <v>2.88315919437213</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.318582604877583</v>
+        <v>-4.317664188466122</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.40817625359834</v>
+        <v>1.408543620162924</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.6343458882782431</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.754807137049298</v>
+        <v>2.755358186896174</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.637926679958085</v>
+        <v>-4.637008263546623</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282211550266398</v>
+        <v>1.282578916830982</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.6343458882782431</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.756580063749557</v>
+        <v>2.757131113596434</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.069732473107872</v>
+        <v>-5.068814056696411</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.096189487038472</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7716818011309712</v>
+        <v>-0.7707633847195101</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.661613503199078</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.304426467240424</v>
+        <v>-5.303508050828963</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>0.9905966643875415</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.765345533901716</v>
+        <v>-0.7644271174902549</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.653700038538722</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.640089114470877</v>
+        <v>-5.639170698059416</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>0.8549121971513256</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8332765193906209</v>
+        <v>-0.8323581029791598</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.611522038901344</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.00371535937119</v>
+        <v>-6.002796942959729</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.7159492594254422</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9314981562577467</v>
+        <v>-0.9305797398462856</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.55907661701531</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.367924325598476</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.5691528213757748</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.226890524145298</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.380544661441734</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.776513102779155</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.404478854518262</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.635479301325977</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.134152939148086</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-7.053089203094987</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.28903384686339</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.635479301325977</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.129338371619546</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.469481077381984</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.1204711477574683</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.635479301325977</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.127332422228424</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.713752478109054</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.03302127813531941</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.635479301325977</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.137591112897103</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-7.919003497345814</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>-0.05297956441368967</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.635479301325977</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.133690678042798</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-8.082583375530199</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>-0.1200065956324421</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.635479301325977</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.132095598097799</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.379244717340397</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.2348921564273132</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.704222437059855</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.09462869258668</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.5659644256497</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.3136063442854375</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.704222437059855</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.090602388052277</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-8.948965814392331</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.466909001104074</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.704222437059855</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.090500286730693</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-9.130835605377365</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.5370854015266575</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.88609222804489</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>1.983949928111102</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.490365927881367</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.6755472272302079</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.88609222804489</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>1.989300231409152</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.540714991335589</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.6877708326547194</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.936441291499112</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>1.967006813293796</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.638334268756985</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.7237767930015089</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-2.034060568920509</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>1.911476997462727</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.785860356762628</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.7798936718821938</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.181586656926152</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.825854900980914</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.990118532092492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.8560837448954972</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.309225601540141</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.754784731331162</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-10.06445150835266</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.8813343809151264</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.453925125474814</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.672447571454795</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.990981676685207</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.8365747467547262</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.380455293807366</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.731901171948685</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-10.16610609407175</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.8920692929618266</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.555579711193909</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.641381742264276</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.40055818808624</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.9930692954692186</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.555579711193909</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.63416257736268</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.50493291911269</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-1.041491378653773</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.659954442220355</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.564865547972836</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.55771907471301</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-1.061490051055348</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.755629928802752</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.508576045861954</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.6837558680813</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.109211039773549</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.73037830599301</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.526420748176914</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.63174035411249</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.084414498499623</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.73037830599301</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.530411083863315</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.77341219583661</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.142558462088012</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.73037830599301</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.528935856964573</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.72382135141178</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.107668714153207</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.680787461568176</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.573743773784346</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.711013958407</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.11559689059798</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.729643236577077</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.531379175132322</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.48516880568759</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-1.015679756474006</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.687716560989913</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.566114253520829</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.36059014935</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.964709149382911</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.687716560989913</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.567253398076888</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.41348543739428</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.9832334904385176</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.682761214901467</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.572860379892064</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.3413522621064</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.9486465160847288</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.682761214901467</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.5785940841307</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.26998586949676</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.9298372214347346</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.611394822291819</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.611676657302624</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-10.17652683551153</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.9023370891535527</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.611394822291819</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.601793175989716</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.909285034643133</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.7972749293055674</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.611394822291819</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.599958615490342</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.811377995966643</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.7584124288084317</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.543409072431262</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.640449750433215</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.787424454990685</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.7481625062725552</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.519455531455305</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.655490381164284</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.523364516667888</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.6557988471051885</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.255395593132509</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.800666027996209</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839728</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.816284893163051</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.3757540313635546</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.255395593132509</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.797878994335908</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.77610059479686</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.359336688129237</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.215211294766318</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.822333197243464</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.612700723857497</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.2946099185327347</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-2.051811423826956</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>1.919739941027839</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.379219501627897</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.1932930008030427</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.818330201597357</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.06775310320345</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.229553110620383</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.136318654712996</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.725426710354821</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.120602987636012</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-8.097277636989496</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.08804097851361403</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.593151236723934</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.195335758561571</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-7.941539304429754</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>-0.02293058480208066</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.437412904164193</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.291593818785053</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.692539505746173</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.08957567589501059</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.437412904164193</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.304500160008712</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.798129495519277</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>-0.08063624961345006</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.543002893937297</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.11317023654563</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.816864397637874</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>-0.03958586858380242</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.548598903597429</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.158356972626638</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.668924356230275</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.1002887747089303</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.528277987688871</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.050670599483605</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.615954833976287</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.08781495206081313</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.475308465434882</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.07373832658252</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.572406427205596</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>-0.07735620144763011</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.475308465434882</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.066777714487427</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.330258033751738</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.03396551031505624</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.475308465434882</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.08124006886857</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.221998896629216</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.07180128562325994</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.475308465434882</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.075772189327765</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-7.098707761812086</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.1186158335606895</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.352017330617752</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.14724496422862</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-7.077558562908642</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.1347764913593918</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.330868131714309</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.167635461808011</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.833793120925198</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.2280633764998203</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.330868131714309</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.163416170155062</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.732030300647903</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.2708928185307542</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.31764906332188</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.173471925110535</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.482179906698828</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.3635750510940863</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.31764906332188</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.166214000094237</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.306287814231396</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.4375310116017079</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.31764906332188</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.169813123614886</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-6.134841351208933</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.5194371028652469</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-1.146202600299417</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.286008507482918</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-6.060551785470594</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.5481734067768795</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-1.071913034561077</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.329602724542218</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-5.996916043236659</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.5783225047247704</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-1.008277292327143</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.372478970936896</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.885489283910739</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.6040874672389345</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-1.008277292327143</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.353673229720692</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.645058787105879</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.7020027425857558</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7678467955222823</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.499674604428486</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.572816218934684</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.7348290836890539</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7678467955222823</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.503603918263305</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879968</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.519817896653296</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.756706996518949</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.7125105365203435</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.537484257581809</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.411013011173569</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.7972270219308335</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.7125105365203435</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.534482328801802</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675943</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.190992213136559</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.8868143781562519</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5712906914523632</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.620793272853205</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-5.058124524073281</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>0.9558556365833861</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5712906914523632</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.636687455655028</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.937951440708782</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.005070714369487</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.4511176080878643</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.709937150114029</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.793279295609045</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.073027674970822</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.3064454629881269</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.806828539735311</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.853154122966737</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.035115235429171</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.366320290345819</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.756941134722122</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.766354625187729</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.092235527863341</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.366320290345819</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.779341628044688</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.768824331649535</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.09132004665203</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.3687899968076251</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.777932205541016</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.837194517973545</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.074978894597128</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3595142977714102</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.794504547437448</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.946651115301141</v>
+        <v>-4.945732698889679</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.021632964297981</v>
+        <v>1.022000330862566</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3595142977714102</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.784941256069339</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.977644274629847</v>
+        <v>-4.976725858218384</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8339452656068858</v>
+        <v>0.8343126321714707</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3595142977714102</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.609650821109726</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.802170014837378</v>
+        <v>-4.801251598425916</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9087022015156609</v>
+        <v>0.9090695680802459</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3595142977714102</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.614218053101514</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.913106267478627</v>
+        <v>-4.912187851067165</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8400697292203685</v>
+        <v>0.8404370957849534</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3595142977714102</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.589960081862721</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.879442722006345</v>
+        <v>-4.878524305594882</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8566665326291869</v>
+        <v>0.8570338991937718</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3258507522991284</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.613289594365995</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.819590102802621</v>
+        <v>-4.818671686391159</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8907799667428087</v>
+        <v>0.8911473333073934</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3258507522991284</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.623461980798127</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.733346639776244</v>
+        <v>-4.732428223364781</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.92022362252722</v>
+        <v>0.9205909890918049</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3258507522991284</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.618408251371988</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.778653459175223</v>
+        <v>-4.777735042763761</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8938766702121537</v>
+        <v>0.8942440367767386</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3666609153083591</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.585697929010975</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.807686563877525</v>
+        <v>-4.806768147466062</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8828153013643347</v>
+        <v>0.8831826679289196</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3666609153083591</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.586249802044077</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.714876082426665</v>
+        <v>-4.713957666015203</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8492121858360442</v>
+        <v>0.8495795524006291</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.2738504338574998</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.571208782805958</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.759265551756092</v>
+        <v>-4.75834713534463</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8333298740288742</v>
+        <v>0.8336972405934588</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.3182399031869275</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.546448577132902</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.646594333519842</v>
+        <v>-4.64567591710838</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8734740698350971</v>
+        <v>0.873841436399682</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.2055686849506773</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.609127016586375</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.623842989996371</v>
+        <v>-4.533298915925707</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.888065903075153</v>
+        <v>0.9242835327034185</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.2055686849506773</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.614618312417043</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.651623387897724</v>
+        <v>-4.56107931382706</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8884509456831509</v>
+        <v>0.9246685753114163</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.2333490828520303</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.60944727544477</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.734624668923002</v>
+        <v>-4.644080594852339</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6936061532736926</v>
+        <v>0.729823782901958</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2519199673792041</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.436660464729119</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.843238747366334</v>
+        <v>-4.75269467329567</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7703101826155658</v>
+        <v>0.8065278122438313</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2519199673792041</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.556810125448324</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.929837330347437</v>
+        <v>-4.839293256276773</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7501837755254477</v>
+        <v>0.7864014051537132</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2519199673792041</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.571323151550647</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.891453667789285</v>
+        <v>-4.800909593718622</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7629566818910767</v>
+        <v>0.7991743115193422</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.2135363048210529</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.591772790427907</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.714337337754119</v>
+        <v>-4.623793263683456</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8305322427504451</v>
+        <v>0.8667498723787106</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.2135363048210529</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.588501819273208</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.759429582587665</v>
+        <v>-4.668885508517001</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8131787365789398</v>
+        <v>0.8493963662072055</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.2754323479904427</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.552047585133488</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.580054161348897</v>
+        <v>-4.489510087278234</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8787158803808612</v>
+        <v>0.9149335100091269</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.118655589819724</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.639900615342333</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.625068374869503</v>
+        <v>-4.534524300798839</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8415176503042088</v>
+        <v>0.8777352799324742</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.1490044851343286</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.60249873348516</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.892072885141938</v>
+        <v>-4.801528811071274</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7404074085341805</v>
+        <v>0.776625038162446</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.3433675231772772</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.491572472998337</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.993270666579111</v>
+        <v>-4.902726592508447</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6991322178558128</v>
+        <v>0.7353498474840783</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.4117763367225964</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.449731106767647</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.960795080408339</v>
+        <v>-4.870251006337675</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7097224138784384</v>
+        <v>0.7459400435067041</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.4117763367225964</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.447331068321964</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.941756952701041</v>
+        <v>-4.851212878630378</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7138623841696023</v>
+        <v>0.7500800137978678</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4699599480537909</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.408945620731492</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.97288358385166</v>
+        <v>-4.882339509780996</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8789936006480354</v>
+        <v>0.9152112302763009</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4699599480537909</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.586527489670172</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.98397560179564</v>
+        <v>-4.896206271114914</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.875390122456577</v>
+        <v>0.9104978547288674</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4946961267436525</v>
+        <v>-0.5078178647876139</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.572519111442389</v>
+        <v>2.564646068616012</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.004232900324598</v>
+        <v>-4.916463569643872</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8732957334419198</v>
+        <v>0.9084034657142102</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4946961267436525</v>
+        <v>-0.5078178647876139</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.578527641839315</v>
+        <v>2.570654599012938</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.856489930089595</v>
+        <v>-4.768720599408869</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.011545569327943</v>
+        <v>1.046653301600233</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3268887695087693</v>
+        <v>-0.3400105075527308</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.758364703972267</v>
+        <v>2.75049166114589</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.958504612620817</v>
+        <v>-4.870735281940091</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9735333178469352</v>
+        <v>1.008641050119226</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3268887695087693</v>
+        <v>-0.3400105075527308</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.761158325503748</v>
+        <v>2.753285282677371</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394736</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.952351906568032</v>
+        <v>-4.864582575887306</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9766567486597073</v>
+        <v>1.011764480931998</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.320736063455985</v>
+        <v>-0.3338578014999465</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.765512297527077</v>
+        <v>2.7576392547007</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.969161204718534</v>
+        <v>-4.881391874037808</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9690135061396168</v>
+        <v>1.004121238411907</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3375453616064867</v>
+        <v>-0.3506670996504481</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.754507195376886</v>
+        <v>2.746634152550509</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.906863205942412</v>
+        <v>-4.819093875261686</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.060268259446886</v>
+        <v>1.095375991719177</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3375453616064867</v>
+        <v>-0.3506670996504481</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.820842749173707</v>
+        <v>2.81296970634733</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992197</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.705073008277254</v>
+        <v>-4.617303677596528</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8495652109023477</v>
+        <v>0.8846729431746381</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1395271694373323</v>
+        <v>-0.1526489074812937</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.648234536864598</v>
+        <v>2.640361494038221</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.645182326634661</v>
+        <v>-4.557412995953935</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9438117158815602</v>
+        <v>0.9789194481538508</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.07963648779473881</v>
+        <v>-0.09275822583870025</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754459178172329</v>
+        <v>2.746586135345952</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319551</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.742922871259635</v>
+        <v>-4.655153540578909</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9193432341476142</v>
+        <v>0.9544509664199046</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.095525765927719</v>
+        <v>-0.1086475039716804</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759553347408584</v>
+        <v>2.751680304582207</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248939</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.919260631382564</v>
+        <v>-4.831491300701838</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8473441109231141</v>
+        <v>0.8824518431954045</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2718635260506484</v>
+        <v>-0.2849852640946098</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.652286672159498</v>
+        <v>2.644413629333121</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.8364116723978</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.842838584950638</v>
+        <v>-4.755069254269912</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8764045475358133</v>
+        <v>0.9115122798081039</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2718635260506484</v>
+        <v>-0.2849852640946098</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650778290199427</v>
+        <v>2.64290524737305</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024968</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.798465453312069</v>
+        <v>-4.710696122631343</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.894016667626677</v>
+        <v>0.9291243998989676</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2274903944120798</v>
+        <v>-0.2406121324560412</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.677265036618004</v>
+        <v>2.669391993791627</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.790511483017297</v>
+        <v>-4.702742152336571</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8971982557445859</v>
+        <v>0.9323059880168763</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2274903944120798</v>
+        <v>-0.2406121324560412</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.677265036618004</v>
+        <v>2.669391993791627</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.742855752456241</v>
+        <v>-4.655086421775515</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9226423049968129</v>
+        <v>0.9577500372691032</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1798346638510241</v>
+        <v>-0.1929564018949856</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.712240231982442</v>
+        <v>2.704367189156065</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326878</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.615171442661945</v>
+        <v>-4.527402111981218</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9786084022892563</v>
+        <v>1.013716134561547</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.05215035405672769</v>
+        <v>-0.06527209210068913</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.793743191233745</v>
+        <v>2.785870148407368</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314554</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.675838033064334</v>
+        <v>-4.588068702383607</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9410964386041727</v>
+        <v>0.9762041708764635</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1338486707752614</v>
+        <v>-0.1469704088192228</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.731478873678497</v>
+        <v>2.72360583085212</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.630999631455936</v>
+        <v>-4.543230300775209</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9631295018581607</v>
+        <v>0.9982372341304515</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1293052378303919</v>
+        <v>-0.1424269758743533</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.738302636056047</v>
+        <v>2.73042959322967</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.731758267212934</v>
+        <v>-4.643988936532207</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9269869871864393</v>
+        <v>0.9620947194587302</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2181308065573973</v>
+        <v>-0.2312525446013587</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.689168234450922</v>
+        <v>2.681295191624545</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.687555430127033</v>
+        <v>-4.599786099446306</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9505477245486367</v>
+        <v>0.9856554568209275</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1739279694714969</v>
+        <v>-0.1870497075154583</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.721569539230299</v>
+        <v>2.713696496403923</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.724534457790476</v>
+        <v>-4.636765127109749</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9341661139525073</v>
+        <v>0.9692738462247981</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1369540676801663</v>
+        <v>-0.1500758057241278</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.742163880774345</v>
+        <v>2.734290837947968</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.744592536655317</v>
+        <v>-4.65682320597459</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9773906475896106</v>
+        <v>1.012498379861901</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1369540676801663</v>
+        <v>-0.1500758057241278</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.793411645957385</v>
+        <v>2.785538603131008</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.704661863477426</v>
+        <v>-4.616892532796699</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9918036214550199</v>
+        <v>1.026911353727311</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.09702339450227598</v>
+        <v>-0.1101451325462374</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.815810754458372</v>
+        <v>2.807937711631995</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.653629770754899</v>
+        <v>-4.565860440074172</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.007164686782301</v>
+        <v>1.042272419054592</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.04599130177974803</v>
+        <v>-0.05911303982370947</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.841378238330159</v>
+        <v>2.833505195503782</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.588405589627693</v>
+        <v>-4.500636258946966</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.050441763325888</v>
+        <v>1.085549495598179</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.0192328793474576</v>
+        <v>0.006111141303496159</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.897700151099187</v>
+        <v>2.889827108272811</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.550978569556559</v>
+        <v>-4.463209238875832</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.061373543653622</v>
+        <v>1.096481275925913</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.02448441737663926</v>
+        <v>0.01136267933267782</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.896812046215977</v>
+        <v>2.8889390033896</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.571090225591267</v>
+        <v>-4.48332089491054</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.054585673570979</v>
+        <v>1.08969340584327</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.03551176237405845</v>
+        <v>0.02239002433009701</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.904685245545668</v>
+        <v>2.896812202719292</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.82869047939355</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.517345411164063</v>
+        <v>-4.429576080483336</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.236641370363072</v>
+        <v>1.271749102635362</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.04557507181452042</v>
+        <v>0.03245333377055898</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.071281002231157</v>
+        <v>3.063407959404779</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714889</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.493553842557921</v>
+        <v>-4.405784511877194</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.366270907023346</v>
+        <v>1.401378639295636</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.06936664042066271</v>
+        <v>0.05624490237670127</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.205668852612659</v>
+        <v>3.197795809786282</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756015</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.467469758294112</v>
+        <v>-4.379700427613385</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.368412516742728</v>
+        <v>1.403520249015019</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.06936664042066271</v>
+        <v>0.05624490237670127</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.197376828626518</v>
+        <v>3.189503785800141</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.463135455237064</v>
+        <v>-4.375366124556337</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.368339433549327</v>
+        <v>1.403447165821617</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2210167437398666</v>
+        <v>0.2078950056959052</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.28656008620182</v>
+        <v>3.278687043375443</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79629317771712</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.454242993843781</v>
+        <v>-4.366473663163054</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.389450823833431</v>
+        <v>1.424558556105722</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2210167437398666</v>
+        <v>0.2078950056959052</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.304114491928611</v>
+        <v>3.296241449102234</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702629</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.622719110813659</v>
+        <v>-4.348697770921581</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.313915424450064</v>
+        <v>1.423523960406895</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1930689080232859</v>
+        <v>0.2229388277398978</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.279200837903247</v>
+        <v>3.297122789733214</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.924919581952075</v>
+        <v>-3.650898242059998</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.663447897451541</v>
+        <v>1.773056433408372</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1227208486528751</v>
+        <v>0.152590768369487</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.307404663737844</v>
+        <v>3.325326615567811</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389901</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.902198478268923</v>
+        <v>-3.628177138376846</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.663200361421707</v>
+        <v>1.772808897378538</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1227208486528751</v>
+        <v>0.152590768369487</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.298068686234748</v>
+        <v>3.315990638064716</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534939</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.042491077806115</v>
+        <v>-3.768469737914038</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.765989447457999</v>
+        <v>1.87559798341483</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.01757175088431751</v>
+        <v>0.0122981688322944</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.372799252363602</v>
+        <v>3.390721204193569</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401677</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.197272084584371</v>
+        <v>-3.923250744692293</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.741154867240343</v>
+        <v>1.850763403197174</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.05093942493879361</v>
+        <v>-0.02106950522218171</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.389856470424563</v>
+        <v>3.40777842225453</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557225</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.264532528606288</v>
+        <v>-3.99051118871421</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.710926045621122</v>
+        <v>1.820534581577953</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1181998689607107</v>
+        <v>-0.08832994924409882</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.346175560000958</v>
+        <v>3.364097511830925</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.242060994567455</v>
+        <v>-3.968039654675378</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.729920812881396</v>
+        <v>1.839529348838227</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.0175056158552605</v>
+        <v>0.04737553557187241</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.437605004535282</v>
+        <v>3.455526956365249</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.793386779707436</v>
+        <v>3.752595490886146</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.426126353051396</v>
+        <v>3.428204813796467</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.242060994567455</v>
+        <v>-3.97151029870804</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.729920812881396</v>
+        <v>1.839244269999503</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.0175056158552605</v>
+        <v>0.04737553557187241</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.419190150037763</v>
+        <v>3.45663013513959</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240622.xlsx
+++ b/tame_output/ON/bt/strategyON_20240622.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-691.9%</t>
+          <t>-692.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.6%</t>
+          <t>458.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-558.7%</t>
+          <t>-568.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>120.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.3%</t>
+          <t>-196.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.4%</t>
+          <t>-300.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-168.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-219.3%</t>
+          <t>-224.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.4%</t>
+          <t>-103.6%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.161955619248791</v>
+        <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251781595428601</v>
+        <v>2.251414228864017</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.5826943518999366</v>
+        <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.466536878581827</v>
+        <v>3.46598582873495</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.528024346393444</v>
+        <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098438403877189</v>
+        <v>2.098071037312605</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2166256247552839</v>
+        <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239979941601484</v>
+        <v>3.239428891754608</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.736515127845128</v>
+        <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035380381035283</v>
+        <v>2.035013014470699</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.008134843303599482</v>
+        <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.135223762469242</v>
+        <v>3.134672712622365</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.98371631261035</v>
+        <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944598657537763</v>
+        <v>1.944231290973179</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.0282881968024119</v>
+        <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.155414524977098</v>
+        <v>3.154863475130221</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.476101340634447</v>
+        <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748751038371857</v>
+        <v>1.748383671807272</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4640968312216848</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.861089900206372</v>
+        <v>2.860538850359495</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.861281731564519</v>
+        <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.593221420812691</v>
+        <v>1.592854054248107</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4640968312216848</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859632439019235</v>
+        <v>2.859081389172359</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.1111524115791</v>
+        <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.495042272261474</v>
+        <v>1.49467490569689</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4278341113912216</v>
+        <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.88315919437213</v>
+        <v>2.882608144525252</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.317664188466122</v>
+        <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.408543620162924</v>
+        <v>1.40817625359834</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6343458882782431</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.755358186896174</v>
+        <v>2.754807137049298</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.637008263546623</v>
+        <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282578916830982</v>
+        <v>1.282211550266398</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6343458882782431</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.757131113596434</v>
+        <v>2.756580063749557</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.068814056696411</v>
+        <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.096189487038472</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7707633847195101</v>
+        <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661613503199078</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.303508050828963</v>
+        <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9905966643875415</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7644271174902549</v>
+        <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653700038538722</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.639170698059416</v>
+        <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8549121971513256</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8323581029791598</v>
+        <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.611522038901344</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.002796942959729</v>
+        <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7159492594254422</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9305797398462856</v>
+        <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.55907661701531</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.367924325598476</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5691528213757748</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.226890524145298</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.380544661441734</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.776513102779155</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.404478854518262</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.635479301325977</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.134152939148086</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.053089203094987</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.28903384686339</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.635479301325977</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.129338371619546</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.469481077381984</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1204711477574683</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.635479301325977</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.127332422228424</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.713752478109054</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03302127813531941</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.635479301325977</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137591112897103</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919003497345814</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05297956441368967</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.635479301325977</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133690678042798</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.082583375530199</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1200065956324421</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.635479301325977</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.132095598097799</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.379244717340397</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2348921564273132</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.704222437059855</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.09462869258668</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.5659644256497</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3136063442854375</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.704222437059855</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.090602388052277</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.948965814392331</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.466909001104074</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.704222437059855</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.090500286730693</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.130835605377365</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5370854015266575</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.88609222804489</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983949928111102</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.490365927881367</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6755472272302079</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.88609222804489</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.989300231409152</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.540714991335589</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6877708326547194</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.936441291499112</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.967006813293796</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.638334268756985</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7237767930015089</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.034060568920509</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.911476997462727</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.785860356762628</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7798936718821938</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.181586656926152</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825854900980914</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.990118532092492</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8560837448954972</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.309225601540141</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754784731331162</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06445150835266</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8813343809151264</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.453925125474814</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.672447571454795</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.990981676685207</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8365747467547262</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.380455293807366</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731901171948685</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16610609407175</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8920692929618266</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.555579711193909</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.641381742264276</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.40055818808624</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9930692954692186</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.555579711193909</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.63416257736268</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50493291911269</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041491378653773</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.659954442220355</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564865547972836</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55771907471301</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061490051055348</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.755629928802752</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508576045861954</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.6837558680813</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109211039773549</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.73037830599301</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.526420748176914</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63174035411249</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084414498499623</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.73037830599301</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.530411083863315</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77341219583661</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142558462088012</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.73037830599301</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528935856964573</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72382135141178</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.107668714153207</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.680787461568176</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573743773784346</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.711013958407</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.11559689059798</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.729643236577077</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.531379175132322</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48516880568759</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.015679756474006</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.687716560989913</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.566114253520829</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36059014935</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.964709149382911</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.687716560989913</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.567253398076888</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41348543739428</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9832334904385176</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.682761214901467</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572860379892064</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.3413522621064</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9486465160847288</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.682761214901467</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.5785940841307</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.26998586949676</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9298372214347346</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.611394822291819</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611676657302624</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17652683551153</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9023370891535527</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.611394822291819</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601793175989716</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.909285034643133</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7972749293055674</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.611394822291819</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599958615490342</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.811377995966643</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7584124288084317</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.543409072431262</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.640449750433215</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.787424454990685</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7481625062725552</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.519455531455305</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.655490381164284</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.523364516667888</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6557988471051885</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.255395593132509</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800666027996209</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.816284893163051</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3757540313635546</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.255395593132509</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797878994335908</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.77610059479686</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.359336688129237</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.215211294766318</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.822333197243464</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.612700723857497</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2946099185327347</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.051811423826956</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919739941027839</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.379219501627897</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1932930008030427</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.818330201597357</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.06775310320345</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.229553110620383</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.136318654712996</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.725426710354821</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120602987636012</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.097277636989496</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08804097851361403</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.593151236723934</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.195335758561571</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.941539304429754</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02293058480208066</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.437412904164193</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291593818785053</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.692539505746173</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08957567589501059</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.437412904164193</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.304500160008712</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.798129495519277</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08063624961345006</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543002893937297</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.11317023654563</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.816864397637874</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03958586858380242</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.548598903597429</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.158356972626638</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.668924356230275</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1002887747089303</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.528277987688871</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050670599483605</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.615954833976287</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08781495206081313</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.475308465434882</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.07373832658252</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.572406427205596</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07735620144763011</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.475308465434882</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.066777714487427</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.330258033751738</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03396551031505624</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.475308465434882</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.08124006886857</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.221998896629216</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07180128562325994</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.475308465434882</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075772189327765</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.098707761812086</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1186158335606895</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352017330617752</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.14724496422862</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.077558562908642</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1347764913593918</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.330868131714309</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167635461808011</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.833793120925198</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2280633764998203</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.330868131714309</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.163416170155062</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732030300647903</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2708928185307542</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.31764906332188</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.173471925110535</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.482179906698828</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3635750510940863</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.31764906332188</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.166214000094237</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.306287814231396</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4375310116017079</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.31764906332188</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169813123614886</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.134841351208933</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5194371028652469</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.146202600299417</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.286008507482918</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.060551785470594</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5481734067768795</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.071913034561077</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329602724542218</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.996916043236659</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5783225047247704</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.008277292327143</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.372478970936896</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.885489283910739</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6040874672389345</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.008277292327143</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353673229720692</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645058787105879</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7020027425857558</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7678467955222823</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499674604428486</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.572816218934684</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7348290836890539</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7678467955222823</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503603918263305</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.519817896653296</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.756706996518949</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7125105365203435</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.537484257581809</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411013011173569</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7972270219308335</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7125105365203435</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.534482328801802</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.190992213136559</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8868143781562519</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5712906914523632</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620793272853205</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.058124524073281</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9558556365833861</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5712906914523632</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636687455655028</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.937951440708782</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.005070714369487</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4511176080878643</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709937150114029</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.793279295609045</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.073027674970822</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3064454629881269</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806828539735311</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.853154122966737</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.035115235429171</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.366320290345819</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756941134722122</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.766354625187729</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.092235527863341</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.366320290345819</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.779341628044688</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.768824331649535</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.09132004665203</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3687899968076251</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.777932205541016</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.837194517973545</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074978894597128</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3595142977714102</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.794504547437448</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.945732698889679</v>
+        <v>-4.946651115301141</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.022000330862566</v>
+        <v>1.021632964297981</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3595142977714102</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784941256069339</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.976725858218384</v>
+        <v>-4.977644274629847</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8343126321714707</v>
+        <v>0.8339452656068858</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3595142977714102</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609650821109726</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.801251598425916</v>
+        <v>-4.802170014837378</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9090695680802459</v>
+        <v>0.9087022015156609</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3595142977714102</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.614218053101514</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.912187851067165</v>
+        <v>-4.913106267478627</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8404370957849534</v>
+        <v>0.8400697292203685</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3595142977714102</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589960081862721</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.878524305594882</v>
+        <v>-4.879442722006345</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8570338991937718</v>
+        <v>0.8566665326291869</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3258507522991284</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.613289594365995</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.818671686391159</v>
+        <v>-4.819590102802621</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8911473333073934</v>
+        <v>0.8907799667428087</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3258507522991284</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.623461980798127</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.732428223364781</v>
+        <v>-4.733346639776244</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9205909890918049</v>
+        <v>0.92022362252722</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3258507522991284</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.618408251371988</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.777735042763761</v>
+        <v>-4.778653459175223</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8942440367767386</v>
+        <v>0.8938766702121537</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3666609153083591</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585697929010975</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.806768147466062</v>
+        <v>-4.807686563877525</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8831826679289196</v>
+        <v>0.8828153013643347</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3666609153083591</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.586249802044077</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.713957666015203</v>
+        <v>-4.714876082426665</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8495795524006291</v>
+        <v>0.8492121858360442</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2738504338574998</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.571208782805958</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.75834713534463</v>
+        <v>-4.759265551756092</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8336972405934588</v>
+        <v>0.8333298740288742</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3182399031869275</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.546448577132902</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.64567591710838</v>
+        <v>-4.646594333519842</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.873841436399682</v>
+        <v>0.8734740698350971</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2055686849506773</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.609127016586375</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.533298915925707</v>
+        <v>-4.534217332337169</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9242835327034185</v>
+        <v>0.9239161661388335</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2055686849506773</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614618312417043</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.56107931382706</v>
+        <v>-4.561997730238522</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9246685753114163</v>
+        <v>0.9243012087468316</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2333490828520303</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.60944727544477</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.644080594852339</v>
+        <v>-4.575554959266236</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.729823782901958</v>
+        <v>0.7572340371363993</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2519199673792041</v>
+        <v>-0.2816726719334193</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436660464729119</v>
+        <v>2.41880884199659</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.75269467329567</v>
+        <v>-4.684169037709567</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8065278122438313</v>
+        <v>0.8339380664782725</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2519199673792041</v>
+        <v>-0.2816726719334193</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556810125448324</v>
+        <v>2.538958502715795</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.839293256276773</v>
+        <v>-4.77076762069067</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7864014051537132</v>
+        <v>0.8138116593881544</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2519199673792041</v>
+        <v>-0.2816726719334193</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.571323151550647</v>
+        <v>2.553471528818118</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.800909593718622</v>
+        <v>-4.732383958132519</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7991743115193422</v>
+        <v>0.8265845657537834</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2135363048210529</v>
+        <v>-0.2432890093752681</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.591772790427907</v>
+        <v>2.573921167695377</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.623793263683456</v>
+        <v>-4.555267628097353</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8667498723787106</v>
+        <v>0.8941601266131518</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2135363048210529</v>
+        <v>-0.2432890093752681</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.588501819273208</v>
+        <v>2.570650196540679</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.668885508517001</v>
+        <v>-4.600359872930898</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8493963662072055</v>
+        <v>0.8768066204416467</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2754323479904427</v>
+        <v>-0.3051850525446579</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.552047585133488</v>
+        <v>2.534195962400958</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.489510087278234</v>
+        <v>-4.420984451692131</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9149335100091269</v>
+        <v>0.9423437642435681</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.118655589819724</v>
+        <v>-0.1484082943739392</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639900615342333</v>
+        <v>2.622048992609804</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.534524300798839</v>
+        <v>-4.465998665212737</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8777352799324742</v>
+        <v>0.9051455341669152</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1490044851343286</v>
+        <v>-0.1787571896885438</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.60249873348516</v>
+        <v>2.584647110752631</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.801528811071274</v>
+        <v>-4.733003175485172</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.776625038162446</v>
+        <v>0.804035292396887</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3433675231772772</v>
+        <v>-0.3731202277314924</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.491572472998337</v>
+        <v>2.473720850265808</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.902726592508447</v>
+        <v>-4.834200956922345</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7353498474840783</v>
+        <v>0.7627601017185193</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4117763367225964</v>
+        <v>-0.4415290412768116</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.449731106767647</v>
+        <v>2.431879484035118</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.870251006337675</v>
+        <v>-4.801725370751573</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7459400435067041</v>
+        <v>0.7733502977411448</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4117763367225964</v>
+        <v>-0.4415290412768116</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.447331068321964</v>
+        <v>2.429479445589434</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.851212878630378</v>
+        <v>-4.782687243044276</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7500800137978678</v>
+        <v>0.7774902680323086</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4699599480537909</v>
+        <v>-0.4997126526080061</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408945620731492</v>
+        <v>2.391093997998963</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.882339509780996</v>
+        <v>-4.813813874194894</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9152112302763009</v>
+        <v>0.9426214845107419</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4699599480537909</v>
+        <v>-0.4997126526080061</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.586527489670172</v>
+        <v>2.568675866937643</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.896206271114914</v>
+        <v>-4.827680635528812</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9104978547288674</v>
+        <v>0.9379081089633083</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5078178647876139</v>
+        <v>-0.537570569341829</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564646068616012</v>
+        <v>2.546794445883483</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.916463569643872</v>
+        <v>-4.84793793405777</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9084034657142102</v>
+        <v>0.9358137199486509</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5078178647876139</v>
+        <v>-0.537570569341829</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570654599012938</v>
+        <v>2.552802976280409</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.768720599408869</v>
+        <v>-4.700194963822767</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.046653301600233</v>
+        <v>1.074063555834674</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3400105075527308</v>
+        <v>-0.3697632121069458</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.75049166114589</v>
+        <v>2.732640038413361</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.870735281940091</v>
+        <v>-4.802209646353989</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.008641050119226</v>
+        <v>1.036051304353666</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3400105075527308</v>
+        <v>-0.3697632121069458</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.753285282677371</v>
+        <v>2.735433659944842</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394736</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.864582575887306</v>
+        <v>-4.796056940301204</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011764480931998</v>
+        <v>1.039174735166438</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3338578014999465</v>
+        <v>-0.3636105060541616</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.7576392547007</v>
+        <v>2.739787631968171</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.881391874037808</v>
+        <v>-4.812866238451706</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.004121238411907</v>
+        <v>1.031531492646348</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3506670996504481</v>
+        <v>-0.3804198042046632</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746634152550509</v>
+        <v>2.72878252981798</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.819093875261686</v>
+        <v>-4.750568239675584</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.095375991719177</v>
+        <v>1.122786245953618</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3506670996504481</v>
+        <v>-0.3804198042046632</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.81296970634733</v>
+        <v>2.795118083614801</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992197</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.617303677596528</v>
+        <v>-4.548778042010426</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8846729431746381</v>
+        <v>0.9120831974090791</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1526489074812937</v>
+        <v>-0.1824016120355088</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.640361494038221</v>
+        <v>2.622509871305692</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.557412995953935</v>
+        <v>-4.488887360367833</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9789194481538508</v>
+        <v>1.006329702388292</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.09275822583870025</v>
+        <v>-0.1225109303929153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746586135345952</v>
+        <v>2.728734512613423</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319551</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.655153540578909</v>
+        <v>-4.586627904992807</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9544509664199046</v>
+        <v>0.9818612206543453</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1086475039716804</v>
+        <v>-0.1384002085258955</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751680304582207</v>
+        <v>2.733828681849678</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.831491300701838</v>
+        <v>-4.762965665115736</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8824518431954045</v>
+        <v>0.9098620974298455</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2849852640946098</v>
+        <v>-0.3147379686488249</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.644413629333121</v>
+        <v>2.626562006600592</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.755069254269912</v>
+        <v>-4.686543618683809</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9115122798081039</v>
+        <v>0.9389225340425447</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2849852640946098</v>
+        <v>-0.3147379686488249</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.64290524737305</v>
+        <v>2.625053624640521</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.710696122631343</v>
+        <v>-4.642170487045241</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9291243998989676</v>
+        <v>0.9565346541334083</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2406121324560412</v>
+        <v>-0.2703648370102563</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.669391993791627</v>
+        <v>2.651540371059098</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.702742152336571</v>
+        <v>-4.634216516750469</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9323059880168763</v>
+        <v>0.9597162422513172</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2406121324560412</v>
+        <v>-0.2703648370102563</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.669391993791627</v>
+        <v>2.651540371059098</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.655086421775515</v>
+        <v>-4.586560786189413</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9577500372691032</v>
+        <v>0.9851602915035442</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1929564018949856</v>
+        <v>-0.2227091064492007</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.704367189156065</v>
+        <v>2.686515566423537</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.527402111981218</v>
+        <v>-4.458876476395116</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.013716134561547</v>
+        <v>1.041126388795988</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06527209210068913</v>
+        <v>-0.09502479665490421</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785870148407368</v>
+        <v>2.768018525674839</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314554</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.588068702383607</v>
+        <v>-4.519543066797505</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9762041708764635</v>
+        <v>1.003614425110904</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1469704088192228</v>
+        <v>-0.1767231133734379</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.72360583085212</v>
+        <v>2.705754208119591</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.543230300775209</v>
+        <v>-4.474704665189106</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9982372341304515</v>
+        <v>1.025647488364892</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1424269758743533</v>
+        <v>-0.1721796804285684</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.73042959322967</v>
+        <v>2.712577970497141</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.643988936532207</v>
+        <v>-4.575463300946105</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9620947194587302</v>
+        <v>0.9895049736931711</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2312525446013587</v>
+        <v>-0.2610052491555738</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.681295191624545</v>
+        <v>2.663443568892016</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163223</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.599786099446306</v>
+        <v>-4.531260463860204</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9856554568209275</v>
+        <v>1.013065711055368</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1870497075154583</v>
+        <v>-0.2168024120696734</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713696496403923</v>
+        <v>2.695844873671394</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.636765127109749</v>
+        <v>-4.470978530836756</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9692738462247981</v>
+        <v>1.035588484733995</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1500758057241278</v>
+        <v>-0.1852479586796887</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.734290837947968</v>
+        <v>2.713187546174632</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.65682320597459</v>
+        <v>-4.491036609701596</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.012498379861901</v>
+        <v>1.078813018371099</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1500758057241278</v>
+        <v>-0.1852479586796887</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.785538603131008</v>
+        <v>2.764435311357671</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.616892532796699</v>
+        <v>-4.451105936523706</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.026911353727311</v>
+        <v>1.093225992236508</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1101451325462374</v>
+        <v>-0.1453172855017984</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.807937711631995</v>
+        <v>2.786834419858659</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.565860440074172</v>
+        <v>-4.400073843801178</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.042272419054592</v>
+        <v>1.108587057563789</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.05911303982370947</v>
+        <v>-0.09428519277927044</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.833505195503782</v>
+        <v>2.812401903730446</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.500636258946966</v>
+        <v>-4.334849662673973</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.085549495598179</v>
+        <v>1.151864134107376</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.006111141303496159</v>
+        <v>-0.02906101165206482</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.889827108272811</v>
+        <v>2.868723816499474</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.463209238875832</v>
+        <v>-4.297422642602839</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.096481275925913</v>
+        <v>1.16279591443511</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01136267933267782</v>
+        <v>-0.02380947362288316</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.8889390033896</v>
+        <v>2.867835711616263</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.48332089491054</v>
+        <v>-4.317534298637548</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.08969340584327</v>
+        <v>1.156008044352467</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02239002433009701</v>
+        <v>-0.01278212862546396</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.896812202719292</v>
+        <v>2.875708910945955</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.429576080483336</v>
+        <v>-4.263789484210343</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.271749102635362</v>
+        <v>1.33806374114456</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03245333377055898</v>
+        <v>-0.002718819185001997</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.063407959404779</v>
+        <v>3.042304667631443</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.405784511877194</v>
+        <v>-4.239997915604201</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.401378639295636</v>
+        <v>1.467693277804833</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05624490237670127</v>
+        <v>0.02107274942114029</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197795809786282</v>
+        <v>3.176692518012945</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.379700427613385</v>
+        <v>-4.213913831340393</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.403520249015019</v>
+        <v>1.469834887524216</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05624490237670127</v>
+        <v>0.02107274942114029</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.189503785800141</v>
+        <v>3.168400494026804</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.375366124556337</v>
+        <v>-4.209579528283345</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.403447165821617</v>
+        <v>1.469761804330814</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2078950056959052</v>
+        <v>0.1727228527403442</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278687043375443</v>
+        <v>3.257583751602106</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.366473663163054</v>
+        <v>-4.200687066890062</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.424558556105722</v>
+        <v>1.490873194614919</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2078950056959052</v>
+        <v>0.1727228527403442</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.296241449102234</v>
+        <v>3.275138157328898</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702629</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.348697770921581</v>
+        <v>-4.369163183859939</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.423523960406895</v>
+        <v>1.415337795231552</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2229388277398978</v>
+        <v>0.1447750170237634</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.297122789733214</v>
+        <v>3.250224503303533</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.650898242059998</v>
+        <v>-3.671363654998356</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.773056433408372</v>
+        <v>1.764870268233029</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.152590768369487</v>
+        <v>0.07442695765335272</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.325326615567811</v>
+        <v>3.27842832913813</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.628177138376846</v>
+        <v>-3.648642551315203</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.772808897378538</v>
+        <v>1.764622732203195</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.152590768369487</v>
+        <v>0.07442695765335272</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.315990638064716</v>
+        <v>3.269092351635035</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.768469737914038</v>
+        <v>-3.788935150852396</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.87559798341483</v>
+        <v>1.867411818239487</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.0122981688322944</v>
+        <v>-0.06586564188383992</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.390721204193569</v>
+        <v>3.343822917763888</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.923250744692293</v>
+        <v>-3.943716157630651</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.850763403197174</v>
+        <v>1.842577238021831</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.02106950522218171</v>
+        <v>-0.09923331593831602</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.40777842225453</v>
+        <v>3.360880135824849</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557225</v>
       </c>
       <c r="C2001" t="n">
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.99051118871421</v>
+        <v>-4.010976601652568</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.820534581577953</v>
+        <v>1.812348416402609</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.08832994924409882</v>
+        <v>-0.1664937599602331</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.364097511830925</v>
+        <v>3.317199225401244</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088376</v>
+        <v>3.76670253008838</v>
       </c>
       <c r="C2002" t="n">
         <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.968039654675378</v>
+        <v>-3.988505067613736</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.839529348838227</v>
+        <v>1.831343183662884</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.04737553557187241</v>
+        <v>-0.03078827514426191</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.455526956365249</v>
+        <v>3.408628669935569</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.752595490886146</v>
+        <v>3.717011931392271</v>
       </c>
       <c r="C2003" t="n">
         <v>3.428204813796467</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.97151029870804</v>
+        <v>-4.065749576385784</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.839244269999503</v>
+        <v>1.801548558928406</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.04737553557187241</v>
+        <v>-0.006223850660684149</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.45663013513959</v>
+        <v>3.424470503400056</v>
       </c>
     </row>
   </sheetData>
